--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026年8月上旬</t>
+          <t>产业与市场数据核验至2026年8月7日；资本化进度与券商关联核验至2026年8月10日</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>01_制图数据：报告图1—图6的原始制图数据；02—07：报告各章表格与正文引用的结构化数据；08_数据来源清单：全部数据的来源出处。</t>
+          <t>01_制图数据：报告图1—图8的原始制图数据；02—07：报告各章表格与正文引用的结构化数据；08_数据来源清单：全部数据的来源出处。</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -708,7 +708,41 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>第二轮更新（2026-08-10）</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>以委托方提供的Wind整理成果为基础重写第六、七章。订正三处：首形科技的主营业务与A2轮跟投主体（应为国泰君安创新投）、智元赴港上市承销团（应为中金＋中信＋摩根士丹利）、卡诺普独家保荐人（应为国泰君安国际）。补充五家国泰海通系公司：三瑞智能、晋拓股份、智谱、镭神技术、飒智智能；补充兆威机电、来福谐波两家已上市产业链公司。新增图7（智元量产爬坡）与图8（国泰海通关联分布）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>口径提示</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>乐聚智能2025年577台为全尺寸人形机器人口径（Omdia与Counterpoint均列全球第四），与赛迪口径下含中小尺寸的约1,000台不同，引用时须注明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>本工作簿的口径与来源均以《数据来源清单》为准。</t>
         </is>
@@ -725,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1675,6 +1709,245 @@
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>数据来源：北京赛迪出版传媒与中国电子报《2025年人形机器人市场研究报告》。优必选2025年年报披露全尺寸人形机器人销量1,079台，与第三方400—1,000台区间存在口径差异；新战略咨询口径下智元为5,168台、宇树与智元份额分别为25%和24%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>图7  智元机器人累计量产下线台数（柱状图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>累计下线台数(台)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2023年（首台样机）</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>公司披露的初期样机数量，与后续累计量产口径不完全一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2025年12月8日</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>灵犀X1/X2 1,846台、远征A1/A2 1,742台、精灵G1/G2 1,412台</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026年3月30日</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>突破万台</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026年6月28日</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>半年内由1万台增至1.5万台</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：智元机器人公开披露及媒体报道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>图8  国泰海通系与人形机器人产业链公司的关联分布（条形图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>关联类型</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>公司/基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>已保荐上市</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>绿的谐波、步科股份、优必选、越疆科技(港)、三瑞智能、乐动机器人、新睿电子、珞石机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>正在保荐/在审/辅导</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>越疆科技(A股)、卡诺普机器人、卧安机器人、晋拓股份(定增)、智谱(辅导)、镭神技术(辅导)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>曾保荐但终止</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>节卡股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>股权投资参股</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>智元机器人、智平方、首形科技、宇树科技、银河通用(间接)、飒智智能、某协作机器人企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>产业基金覆盖</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>只</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>中际旭创产业基金、江城神工基金、科创主题基金矩阵、恒旭资本第四期、上海AI母基金、海通中小企业发展基金、浦东引领区海通母基金等</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：本报告基于表12至表15统计。前四项单位为家、末项为只；产业基金多为综合性股权投资基金，机器人仅为其投资方向之一。</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4758,27 +5031,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>约4000（第三方）/累计5000（自主披露）</t>
+          <t>约4000（赛迪）/5168（新战略）</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>10.5亿元（2025年）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>未公开披露</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>未公开披露</t>
-        </is>
-      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>灵犀X1/X2、远征A1/A2、精灵G1/G2</t>
+          <t>灵犀X1/X2/D1、远征A1/A2、精灵G1/G2</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>截至2025/12/8累计交付5,000台：灵犀1,846台、远征1,742台、精灵1,412台；全球份额23.5%。来源：公司披露、第三方统计</t>
+          <t>2023年营收约30万元、2024年约0.6亿元、2025年10.5亿元（同比增长近20倍）。累计量产下线：2025/12/8达5,000台（灵犀1,846、远征1,742、精灵1,412）、2026/3/30达10,000台、2026/6/28达15,000台。来源：公司披露、赛迪、新战略咨询</t>
         </is>
       </c>
     </row>
@@ -5463,6 +5736,300 @@
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>注：特斯拉产能规划历史上多次延期，上述目标为方向性参考。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>4.4 智元机器人专项（对应报告5.2节、图7）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>公司沿革</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>成立于2023年2月，由彭志辉（稚晖君）与邓泰华共同创立；现定位为"具身智能基础模型公司"</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>产品线—远征系列</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>A1/A2，全尺寸双足，强调长距离行走与复杂环境适应，面向工业搬运、巡检、导览、展示；2024年8月发布远征A2并进入商用交付</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>产品线—灵犀系列</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>X1/X2及D1 Ultra／Pro，覆盖人形、轮式与臂台一体设备；X2身高约1.3米；面向仓储、制造、服务场景的操作与搬取</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>产品线—精灵系列</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>G1/G2，中小型轮式双臂，偏向开发、教学与实验验证，作为高校与企业的具身平台</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>灵渠OS，原生适配具身智能的开源操作系统</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>基座模型</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>启元大模型GenieOperator-1，2026年3月10日发布，融合多模态大模型与混合专家系统</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>战略规划</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2026年进入"部署态"阶段，推出AIMA全栈生态开发平台，全面开放"1+3+X"架构</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>生态投入</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>"元苼生态计划"，未来五年投入20多亿元，扶持科研学术、教育人才、生态伙伴与开发者社区</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>供应链体系</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>建立"全球首个具身智能机器人标准化供应链体系"（A链），覆盖上下游全环节；量产依托上海本地"半小时供应链"</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>订单与产能</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>年度订单需求超10万台，对应规划产能达10万台级；有报道指1.5万台量产背后产业链已出现承压</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>资本化—A股平台</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>2025/7/8受让上纬新材29.99%；9/23完成过户；"协议转让＋部分要约"合计21亿元取得控股权，智元恒岳及一致行动人合计持股63.62%</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>上纬新材公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>资本化—港股IPO</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026/7/24正式启动赴港上市流程，中金公司＋中信证券＋摩根士丹利承销；投资人称目标估值400亿—500亿港元</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>与国泰海通的关系</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资曾参投智元机器人融资</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Wind整理成果</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>说明：本工作表新增，对应报告第5.2节的智元机器人专项分析与图7。</t>
         </is>
       </c>
     </row>
@@ -5477,20 +6044,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人形机器人产业链企业资本化进度（对应报告第6章、表8—表11）</t>
+          <t>人形机器人产业链企业资本化进度（对应报告第6章、表8—表10）</t>
         </is>
       </c>
     </row>
@@ -5509,20 +6077,25 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>上市进度</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>交易所/代码</t>
+          <t>上市地与时间</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>保荐机构</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>核心业务</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>公开财务及估值信息</t>
         </is>
@@ -5536,20 +6109,25 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>已上市</t>
+          <t>09880.HK</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>港交所 09880</t>
+          <t>港交所，2023年12月</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>国泰君安国际（联席保荐）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>全尺寸工业人形机器人及教育/物流/康养机器人</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>2025年营收20.01亿元（+53.3%）；全尺寸人形收入8.2亿元、销量1,079台；年度订单接近14亿元</t>
         </is>
@@ -5558,724 +6136,1300 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>越疆科技</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026/3/20受理，7月初获证监会同意注册（104天）；2026/8/6公告发行价，8/10网上网下申购；保荐人（主承销商）中信证券</t>
+          <t>02432.HK</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板 688836</t>
+          <t>港交所，2024年12月</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>四足机器人与人形机器人</t>
+          <t>国泰君安国际（联席保荐）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2025年营收17.08亿元、扣非归母净利6.001亿元、毛利率60.27%；发行4,044.6434万股（占发行后10%），发行价150.80元/股，发行后市值约609亿元，募资总额约60.99亿元，发行市盈率219.23倍（行业平均38.56倍）；战略配售808.9286万股，含社保基金、深度求索、中国石油集团、南方电网</t>
+          <t>协作机器人，港股18C首家H股</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>截至2025年协作机器人累计出货超10万台，全球份额13.2%居首</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>来福谐波</t>
+          <t>绿的谐波</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026/1/2递表，5/29证监会备案，6/14通过聆讯，6/22—25招股，6/30挂牌</t>
+          <t>688017.SH</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>港交所 03952</t>
+          <t>科创板，2020年8月</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>谐波减速器、关节模组、机械臂、自动化工作站</t>
+          <t>国泰君安（保荐承销）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2023—2025年营收0.95/1.08/2.61亿元；2025年谐波减速器销量29.15万台、均价571元/台、毛利率24.6%；三年连亏，2025年亏损1.71亿元；发行前估值约15亿元；股东含联想、国开基金、紫金矿业</t>
+          <t>谐波减速器、机电一体化产品及关节模组</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收5.71亿元（+47.31%）、归母净利1.24亿元（+121.42%）、销量42.52万台（+72.48%）。2022年度定增及持续督导由中信证券承做</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>乐动机器人</t>
+          <t>步科股份</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026年5月上市；国泰君安国际（国泰海通集团）任联席保荐人、保荐人兼整体协调人，海通国际共同参与</t>
+          <t>688160.SH</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>港交所主板</t>
+          <t>科创板，2020年11月</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>激光雷达及机器人核心传感与解决方案</t>
+          <t>海通证券（保荐承销）</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>总集资额约8.8亿港元</t>
+          <t>伺服系统与无框力矩电机</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2025年无框力矩电机销量约8.3万台（+247.84%）；2024年定增仍由海通证券保荐，现由国泰海通持续督导</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>绿的谐波</t>
+          <t>乐动机器人</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>已上市</t>
+          <t>01236.HK</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板 688017</t>
+          <t>港交所，2026年5月11日</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>谐波减速器、机电一体化产品及关节模组</t>
+          <t>海通国际＋国泰君安国际（联席保荐）</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2025年营收5.71亿元（+47.31%）、归母净利1.24亿元（+121.42%）；谐波减速器及金属部件销量42.52万台（+72.48%）；机电一体化收入0.74亿元（+41.28%）</t>
+          <t>激光雷达及机器人核心传感与解决方案</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>总集资额约8.8亿港元；上市首日涨约102%，公开发售认购约6,707倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>珞石机器人</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>03752.HK</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2026年7月9日</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>中金公司＋国泰君安国际（联席保荐）</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>工业机器人与协作机器人</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>港股18C特专科技公司</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>5.2 在审、已问询或已递表（对应表9）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>上市进度</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>交易所/板块</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>核心业务</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>公开财务及估值信息</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>北交所，2026年6月5日</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（独家保荐）</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>工业机器人控制系统</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>国家级高新技术企业；受理到上市约12个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>三瑞智能</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>301696.SZ</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>创业板，2026年4月10日</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（保荐承销）</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>无人机电动动力系统及机器人动力系统（电机、模组）</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>发行4,001万股；按2024年销售额计全球民用无人机电动动力系统份额7.1%、第二</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>乐聚智能</t>
+          <t>兆威机电</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026/5/19受理，5/26已问询；保荐人东方证券；首家适用创业板第四套上市标准获受理</t>
+          <t>02692.HK</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>港交所，2026年3月9日</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>轻量化人形机器人整机及具身智能解决方案</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>拟募资26亿元；2025年出货约1,000台；预计最早2028年盈利；股东含腾讯、深创投</t>
+          <t>微型传动系统与灵巧手模组</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>发行价71.28港元/股，公开发售认购1,536.76倍，净募资约18.28亿港元，基石含高瓴；上市后一度破发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>云深处科技</t>
+          <t>来福谐波</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2025/12/23辅导备案，2026/5/18受理；保荐机构中信建投证券</t>
+          <t>03952.HK</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>港交所，2026年6月30日</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>高负载四足机器人及人形机器人，电力与矿山巡检</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>拟募资25.03亿元；四足机器人领域收入超波士顿动力，已扭亏为盈；市场估值参考约139亿元</t>
+          <t>谐波减速器、关节模组、机械臂、自动化工作站</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收2.61亿元、销量29.15万台、均价571元/台、亏损1.71亿元；发行前估值约15亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>宇树科技</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>688836.SH</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>科创板，2026年7月2日注册生效</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>中信证券（保荐承销）</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>四足机器人与人形机器人</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收17.08亿元、扣非归母净利6.001亿元、毛利率60.27%；发行价150.80元/股，发行后市值约609亿元，募资约60.99亿元</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>5.3 辅导备案或已完成股改（对应表10）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件；各公司年报及公告。本报告复核后补充三瑞智能、兆威机电、来福谐波，并订正绿的谐波、步科股份的保荐机构归属。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>5.2 在审、已受理或已递表（对应表9）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>资本化进度</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>目标市场</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>保荐机构</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>核心业务</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>公开财务及估值信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>傅利叶智能</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>完成E轮融资与股改，已启动科创板上市辅导准备与申报</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>A股科创板</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>康复机器人切入通用人形，GR系列</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>已实现数百台商业交付；尚处辅导阶段，未形成公开招股书</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>银河通用</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>已完成股改，最新一轮被视为Pre-IPO轮，计划2026下半年递交港股申请</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>港股</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>轮式双臂人形机器人及具身智能大模型</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>2026/3完成25亿元D轮（国家大基金参与），累计融资超70亿元，估值约260亿元</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>公开信息</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>众擎机器人</t>
+          <t>越疆科技（A股）</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>已完成股改，明确上市计划</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>未明确</t>
+          <t>2026/4/27受理，7/22过会</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PM01等中小尺寸双足</t>
+          <t>国泰海通（独家保荐）</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>估值超100亿元</t>
+          <t>协作机器人、多足与人形机器人</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>大湾区首单H股回A，受理到上会86天；拟募资约12亿元（多足5.5亿、人形2.5亿、营销1亿、补流3亿）；创业板第三套标准</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>松延动力</t>
+          <t>卧安机器人</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>已完成股改</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>未明确</t>
+          <t>已通过聆讯并完成上市备案</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>N2等中小尺寸双足</t>
+          <t>国泰君安国际＋华泰国际（联席保荐）</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2025年总订单超2,500台，合同额超1亿元</t>
+          <t>服务机器人（智能家居执行终端）</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>星海图</t>
+          <t>卡诺普机器人</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>已完成股改，最新一轮被视为Pre-IPO轮</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>未明确</t>
+          <t>2025/11/17首次递表，2026年6月再次递表</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>具身智能整机及模型</t>
+          <t>国泰君安国际（独家保荐）</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>估值超100亿元</t>
+          <t>工业、协作及具身智能机器人，型号超70款</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>按2025年收入计为中国焊接机器人制造商第一（弗若斯特沙利文）；18C公司；股东含北极光创投、双环传动</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>魔法原子</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>推进上市准备，最快2026年登陆二级市场</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>未明确</t>
+          <t>2026/7/24正式启动赴港上市流程</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>人形机器人整机</t>
+          <t>中金公司＋中信证券＋摩根士丹利（承销）</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>未公开披露拟募金额和发行比例</t>
+          <t>远征/灵犀/精灵三大产品线及具身智能基座模型</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收10.5亿元；累计量产下线1.5万台；投资人称目标估值400亿—500亿港元</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>新剑传动、智同科技、纽氏达特、金力传动</t>
+          <t>乐聚智能</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>已签署辅导协议并报送材料</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>A股</t>
+          <t>2026/5/19受理，5/26已问询</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>RV减速器及精密传动部件</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>均处辅导阶段，未形成公开招股书</t>
+          <t>轻量化人形机器人</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2025年全尺寸Kuavo系列销量577台（2024年32台），Omdia与Counterpoint列全球第四；2025年营收2.58亿元，三年营收CAGR 118.68%；最近一轮投后估值43.27亿元；拟募资26亿元，创业板第四套标准首单</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>云深处科技</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>2025/12/23辅导备案，2026/5/18受理</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>高负载四足机器人及人形机器人</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收3.37亿元并已盈利；拟募资25.03亿元</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>5.4 通过上市公司平台实现资本化（对应表11）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>5.3 辅导备案或已完成股改（对应表10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>资本化方式</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>关键时点</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>交易对价与比例</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>资本化进度</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>辅导机构</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>核心业务</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>公开财务及估值信息</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>协议转让＋部分要约收购取得A股上市公司控股权</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>2025/7/8受让29.99%；2025/9/23完成过户登记</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>合计21亿元取得上纬新材（688585.SH）66.99%控股权，邓泰华成为上市公司实际控制人</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>上纬新材2024年营收14.94亿元，对应约1.4倍市销率；要约价7.78元/股，2025/9/24收盘价112.7元/股；公司回应称不构成重组上市</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>5.5 资本化整体统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>纽氏达特</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2025/12/3辅导备案</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>东方证券</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>精密传动部件（RV减速器等）</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>与巨蟹同属传动环节</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>天链机器人</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>科创板辅导中（第四期）</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>华安证券</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>进入IPO辅导/申报/聆讯/发行阶段的人形机器人核心企业</t>
+          <t>傅利叶智能</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>完成E轮融资与股改，已启动科创板辅导准备</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>截至2026年7月</t>
+          <t>GR系列全尺寸人形机器人</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>已实现数百台商业交付</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>由康复机器人切入</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>机器人相关企业A股+港股排队数量</t>
+          <t>银河通用</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>&gt;38</t>
+          <t>已完成股改，计划2026下半年递交港股申请</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>轮式双臂人形机器人及具身智能大模型</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>2026/3完成25亿元D轮（国家大基金参与），累计融资超70亿元，估值约260亿元</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本（海通开元为LP）间接持有</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>港股排队机器人相关企业</t>
+          <t>星海图</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>接近50</t>
+          <t>已完成股改，最新一轮视为Pre-IPO轮</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>具身智能整机及模型</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>估值超100亿元</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>具身智能百亿估值独角兽数量</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>13</v>
+          <t>松延动力</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>已完成股改</t>
+        </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>2026年3月</t>
+          <t>人形机器人本体与仿生人脸</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>2025年总订单超2,500台、合同额超1亿元</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026年前5个月国内具身智能融资起数</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>437</v>
+          <t>众擎机器人</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>已完成股改，明确上市计划</t>
+        </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>起</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>2026年1—5月</t>
+          <t>PM01等中小尺寸双足</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>PM01售价8.8万元；与多伦科技2,000台三年框架协议；估值超100亿元</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026年前5个月国内具身智能融资规模</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>489</v>
+          <t>智平方</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>已完成股改</t>
+        </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>2026年1—5月</t>
+          <t>AGI原生通用智能机器人</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>2026/2 B轮超10亿元后估值超100亿元；2026/6新融资50亿元后估值超200亿元</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通B轮联合投资</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>科创板第五套标准对具身智能企业的市值要求</t>
+          <t>星动纪元</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>≥40</t>
+          <t>Pre-IPO轮融资25亿元</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>具身智能整机，外销灵巧手与半身模组</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>科创板新政</t>
+          <t>估值突破百亿元；总订单超5亿元</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>募资规模：宇树（实际）/乐聚（拟）/云深处（拟）</t>
+          <t>首形科技</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>60.99/26/25.03</t>
+          <t>2026/4完成A1轮、7/21完成A2轮，均数亿元</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>超仿生类人机器人与仿生情感交互（高仿真"脸"）</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>A2轮由中信金石与吉利资本联合领投，国泰君安创新投等跟投</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>魔法原子</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>推进上市进程</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>最快可能2026年登陆二级市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；公开融资报道。本报告复核后订正首形科技的主营业务及A2轮跟投主体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>5.4 通过上市公司平台资本化 / IPO终止</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>关键时点</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>交易或终止要点</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>核心业务</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>智元机器人</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>取得A股上市公司控制权</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2025/7/8受让29.99%；2025/9/23完成过户</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>"协议转让＋部分要约"合计21亿元取得上纬新材（688585.SH）控股权，智元恒岳及一致行动人合计持股63.62%，邓泰华成为实际控制人；公司称不构成重组上市</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机与具身智能</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>叠加2026/7启动的赴港IPO，形成"A股控股平台＋H股IPO"双资本布局</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>节卡股份</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>科创板IPO终止</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2023/5受理；2025/12/19撤回，上交所终止审核</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>原计划募资近7亿元；期间多次因财务数据过期中止审核；研发独立性、核心零部件依赖外采、募投产能消化受问询</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>保荐人为国泰海通证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：上纬新材公告；上交所审核信息；公开报道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>5.5 资本化整体统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>进入IPO辅导/申报/聆讯/发行阶段的人形机器人核心企业</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>&gt;20</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>截至2026年7月</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>公开统计</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>中国人形机器人产业股权融资额</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>889</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2026年1—4月</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通研究</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>已远超2025年全年</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2025年行业融资事件</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>&gt;200</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>笔</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>新战略咨询</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>总额超500亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>具身智能百亿估值独角兽数量</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2026年3月</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>公开统计</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>科创板第五套标准对具身智能企业的市值要求</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>≥40</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>现行</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>科创板新政</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>创业板第四套标准亦已开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>募资规模：宇树（实际）/乐聚（拟）/云深处（拟）/越疆A股（拟）</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>60.99/26/25.03/12</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>2026年</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>发行公告与交易所公告</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6290,583 +7444,1542 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>与国泰海通相关的机器人产业链公司（对应报告第7章、表12—表14）</t>
+          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表11—表15）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>6.1 国泰海通投行业务整体位置</t>
+          <t>6.1 券商谱系（对应表11）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>指标</t>
+          <t>券商主体</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>存续时间</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>口径</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
+          <t>与人形机器人产业链的关系</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>A股IPO保荐上市数量</t>
+          <t>国泰证券</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>13单</t>
+          <t>1992/9—1999/8</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>行业第一，市占率约18.3%，较第二名领先4单</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>公开统计</t>
-        </is>
-      </c>
+          <t>在上海成立，国泰君安前身之一。存续期间人形机器人产业尚未兴起，无直接保荐或投资关联</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>A股IPO承销金额</t>
+          <t>君安证券</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>646亿元</t>
+          <t>1992/10—1999/8</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>行业第三</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>公开统计</t>
-        </is>
-      </c>
+          <t>在深圳成立，国泰君安前身之一。存续期间人形机器人产业尚未兴起，无直接保荐或投资关联</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>IPO受理家数及在审家数</t>
+          <t>国泰君安证券</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>并列前二</t>
+          <t>1999/8—2025/3</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>与华泰联合并列</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>公开统计</t>
-        </is>
-      </c>
+          <t>2015年A股上市（601211.SH），2017年H股上市（2611.HK）。保荐绿的谐波、优必选、越疆科技（港股经国泰君安国际）等</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>公司沿革</t>
+          <t>海通证券</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2025/3/14合并</t>
+          <t>1988—2025/3</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安证券与海通证券合并为国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>公开信息</t>
-        </is>
-      </c>
+          <t>2007年A股上市（600837.SH），2012年H股上市（6837.HK）。保荐步科股份、新睿电子等</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2025/3合并、4月更名至今</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安换股吸收合并海通证券，注册资本176.3亿元，净资产行业第一</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>6.2 保荐与承销业务（对应表12）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>业务类型</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>与国泰海通的关系</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>业务与产业链定位</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>资料来源：各券商公开披露。国泰证券与君安证券的存续期远早于人形机器人产业兴起，本表所列关联均发生于国泰君安、海通证券及国泰海通期间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>6.2 整体投行位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>乐动机器人</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>港股IPO保荐</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2026年5月港交所主板上市，国泰海通集团下属国泰君安国际担任联席保荐人、保荐人兼整体协调人，海通国际共同参与，总集资额约8.8亿港元</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>激光雷达及机器人核心传感与解决方案，属机器人感知环节</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>公开报道</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>晋拓科技（603211.SH）</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>再融资保荐</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通证券担任2026年度向特定对象发行股票的保荐人（主承销商）</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>机器人零部件，核心产品覆盖机器人手臂、腿部、关节臂等结构部件</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>上交所披露的发行保荐书</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>新睿电子</t>
+          <t>A股IPO保荐上市数量</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>北交所IPO保荐</t>
+          <t>13单，行业第一，市占率约18.3%</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券担任向不特定合格投资者公开发行股票并在北交所上市的保荐人（主承销商）</t>
+          <t>2026年上半年</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>国家级高新技术企业，专注工业机器人控制系统</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>公开披露的上市保荐书</t>
-        </is>
-      </c>
+          <t>券商IPO保荐半年度统计</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>三瑞智能</t>
+          <t>A股IPO承销金额</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>A股IPO保荐</t>
+          <t>646亿元，行业第三</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券担任南昌三瑞智能科技股份有限公司创业板IPO的保荐人（主承销商）</t>
+          <t>2026年上半年</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>智能装备制造</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>深交所披露的上市保荐书</t>
-        </is>
-      </c>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IPO受理与在审家数</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>与华泰联合并列前二</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026年上半年</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>6.3 上市辅导业务（对应表13）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>备案时间</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>辅导情况</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>业务定位与相关性</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>镭神技术（深圳）股份有限公司</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2026/4/15</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>辅导机构为国泰海通证券，已在深圳证监局办理辅导备案登记</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>成立于2017年10月，为光通信、半导体行业提供精密装备与系统化解决方案；精密耦合设备国内市占率超50%，累计交付高精密设备超600台。属精密装备制造，与机器人产业链非直接相关</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>证监局备案公示、公开报道</t>
-        </is>
-      </c>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>前沿产业（AI、集成电路等）累计投资</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>305个项目、约200亿元</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>截至2026年</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通公开披露</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>累计服务科创板上市企业</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>107家、承销规模超2,100亿元，行业第一</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>截至2026年</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通公开披露</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>智谱</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2026年2月公开</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>撤回2025年4月备案并重新备案，辅导机构变更为国泰海通证券与中金公司</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>人工智能大模型企业，与具身智能"大脑"层在算法上存在关联</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>证监会官网、公开报道</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>上海图灵智算量子科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>2026/7/24签约，8/5备案</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>与国泰海通证券签署IPO辅导协议，在上海证监局完成备案</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>量子计算与智能算力相关企业</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>上海证监局备案公示</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>6.3 已保荐上市（对应表12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>上市地与时间</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>保荐角色</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>归属主体</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>注：截至统计日，未检索到国泰海通担任人形机器人整机或关节模组企业辅导机构的公开信息。</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>绿的谐波</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>688017.SH</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>科创板，2020年8月</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>谐波减速器国内龙头</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>步科股份</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>688160.SH</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>科创板，2020年11月</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>海通证券</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>伺服与无框力矩电机</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>6.4 股权投资业务（对应表14）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>被投企业</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>投资时点</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>投资情况</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>企业基本情况与产业链定位</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>优必选</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>09880.HK</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2023年12月</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人第一股</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>越疆科技</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>02432.HK</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2024年12月</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人第一股，18C首家H股</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>智平方（深圳智平方科技有限公司）</t>
+          <t>三瑞智能</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026/2/23</t>
+          <t>301696.SZ</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>B轮系列融资规模超10亿元，投资方包括百度战投、中国中车、沄柏资本、国泰海通等</t>
+          <t>创业板，2026年4月10日</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>AGI原生通用智能机器人企业，成立于2023年4月；B轮后估值超100亿元，为深圳首家估值超百亿元的具身智能独角兽；2026年6月完成50亿元新融资，估值超200亿元；AlphaBot系列2025年12月单月交付百台级，自建产线年产千台，2026年规划万台。属人形机器人整机（轮式双臂）环节</t>
+          <t>保荐承销</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>公开融资报道</t>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。无人机与机器人动力系统（电机、模组）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>飒智智能（上海飒智智能科技有限公司）</t>
+          <t>乐动机器人</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>01236.HK</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2026年5月11日</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>海通国际＋国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>集资约8.8亿港元，首日涨约102%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>北交所，2026年6月5日</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（原海通承做）</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>工业机器人控制系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>珞石机器人</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>03752.HK</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2026年7月9日</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>18C特专科技公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>6.4 正在保荐、在审或辅导（对应表13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>归属主体</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>业务定位与相关性</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>越疆科技（A股）</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>创业板IPO（H股回A）</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026/4/27受理，7/22过会</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人，拟募资12亿元含人形机器人技术提升2.5亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>卡诺普机器人</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>港交所18C上市</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2025/11/17首次递表，2026年6月再次递表</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>中国焊接机器人制造商第一，已布局具身智能机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>卧安机器人</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>港交所上市</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>已通过聆讯并完成上市备案</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际（与华泰国际）</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>服务机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>晋拓股份</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026年度定增</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>保荐人（主承销商）</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>A股IPO辅导</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月重新办理辅导备案</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>联合辅导机构</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>镭神技术</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>A股IPO辅导</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026/4/15深圳证监局辅导备案</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>辅导机构</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。光通信与半导体精密装备，与机器人产业链非直接相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>6.5 曾保荐但已终止（对应报告7.4节）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>原目标板块</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>受理时间</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>终止时间</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>原保荐机构</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>终止原因指向</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>节卡股份</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2023年5月</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2025年12月19日撤回，上交所终止审核</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>6.6 股权投资参股（对应表14）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>被投企业</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>投资主体</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>轮次/方式</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>企业定位</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>智元机器人</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>合并前</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>参与融资</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机与具身智能基座模型</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月启动赴港IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>智平方</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>B轮联合投资</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>AGI原生通用智能机器人</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>首形科技</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>A2轮跟投</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>超仿生类人机器人与仿生情感交互</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>宇树科技</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证裕投资</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>IPO跟投</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>四足与人形机器人</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>银河通用</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本（海通开元为该基金LP）</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>2024—2025年</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>间接持有</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>轮式双臂人形机器人</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>估值约260亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>飒智智能</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>海通开元（与国元股权联合投资）</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
           <t>A++及A+++轮</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>数亿元融资，由海通开元（现国泰海通体系内私募股权投资平台）与国元股权联合投资</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>智能移动共融机器人技术及产品的研发、集成与应用；产品包括多模态协同作业机器人、高精度上下料移动作业复合机器人、高柔性类人作业移动双臂机器人。属工业/复合机器人整机环节</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>公开融资报道</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>注：证券公司私募股权子公司的投资组合并非全部对外披露，本表仅覆盖可公开检索到的案例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>6.5 研究覆盖（非业务关系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>智能移动共融机器人</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>某协作机器人研发及生产企业</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>海通创新证券投资</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>0.15亿元</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>6.7 产业基金布局（对应表15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>基金名称</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>设立/备案时间</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>管理人与主要参与方</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>投资方向</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通中际旭创产业基金</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>首期15亿元</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>2025年9月设立、11月备案</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>光通信、机器人、人工智能</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通江城神工基金</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>首期2亿元</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>机器人、智能制造</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>科创主题基金矩阵</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>累计超700亿元</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资等</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>科技创新（含机器人）</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>综合性基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本第四期旗舰基金</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>首轮关账超20亿元</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>已投银河通用机器人</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通为LP而非GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>上海三大先导产业母基金（人工智能）</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>225.01亿元</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通仅为出资方之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>海通中小企业发展基金</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>总规模20亿元</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>海通开元；LP含国家中小企业基金与地方国资</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>中早期创业公司（含机器人）</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>综合性基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>浦东引领区海通母基金等</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>140亿元</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>海通开元</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>TMT、先进制造等</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>综合性母基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>6.8 研究覆盖（非业务关系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>事项</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>行业观点</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通证券看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>公开研报报道</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>行业数据</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>个股观点</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>2026年4月将优必选目标价上调至184.77港元</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>公开研报报道</t>
         </is>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -102,19 +102,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -742,7 +739,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>本工作簿的口径与来源均以《数据来源清单》为准。</t>
         </is>
@@ -772,7 +769,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>报告图1—图6制图数据</t>
+          <t>报告图1—图8制图数据</t>
         </is>
       </c>
     </row>
@@ -808,7 +805,7 @@
           <t>旋转执行器（无框力矩电机+谐波减速器+编码器）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -825,7 +822,7 @@
           <t>线性执行器（行星滚柱丝杠+力矩电机）</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -838,7 +835,7 @@
           <t>灵巧手</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -851,7 +848,7 @@
           <t>计算与感知</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
@@ -864,7 +861,7 @@
           <t>结构件与电池</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -877,7 +874,7 @@
           <t>其他（线束/外壳/装配等）</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
@@ -894,7 +891,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="3" t="n">
         <v>100</v>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -902,7 +899,7 @@
       <c r="E11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>数据来源：行业研究机构公开测算及券商研究报告整理。硬件成本约占整机成本60%—70%。</t>
         </is>
@@ -940,7 +937,7 @@
           <t>国产厂商份额  2020年</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="3" t="n">
         <v>48.71</v>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
@@ -957,7 +954,7 @@
           <t>国产厂商份额  2021年</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="3" t="n">
         <v>55.15</v>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -974,7 +971,7 @@
           <t>国产厂商份额  2024年</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="3" t="n">
         <v>75.11</v>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
@@ -991,7 +988,7 @@
           <t>TOP4合计份额  2023年</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="3" t="n">
         <v>59.36</v>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1008,7 +1005,7 @@
           <t>TOP4合计份额  2024年</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="3" t="n">
         <v>64.13</v>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
@@ -1025,7 +1022,7 @@
           <t>（参考）来福谐波中国市占率 2025年</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1042,7 +1039,7 @@
           <t>（参考）全球产能 2024年</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="3" t="n">
         <v>489.7</v>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
@@ -1054,7 +1051,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>数据来源：高工机器人（GGII）《全球谐波减速器市场"沉浮录"》，2025年6月11日；来福谐波港交所上市文件。左右两组份额统计边界不同，不可直接换算。</t>
         </is>
@@ -1100,10 +1097,10 @@
           <t>2025年营业收入</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="3" t="n">
         <v>5.71</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="3" t="n">
         <v>2.61</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1123,10 +1120,10 @@
           <t>2025年归母净利润</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="3" t="n">
         <v>-1.71</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1146,10 +1143,10 @@
           <t>2025年谐波减速器（及金属部件）销量</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="3" t="n">
         <v>42.52</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="3" t="n">
         <v>29.15</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1170,7 +1167,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="3" t="n">
         <v>571</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1191,7 +1188,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n"/>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -1211,7 +1208,7 @@
           <t>2025年机电一体化业务收入</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="3" t="n">
         <v>0.74</v>
       </c>
       <c r="C32" s="3" t="n"/>
@@ -1227,7 +1224,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>数据来源：绿的谐波（688017.SH）2025年年度报告；来福谐波（03952.HK）港交所上市文件及媒体报道。两者销量口径不完全一致。</t>
         </is>
@@ -1273,7 +1270,7 @@
           <t>2024年</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="3" t="n">
         <v>0.28</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1298,7 +1295,7 @@
           <t>2025年</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1323,7 +1320,7 @@
           <t>（对照）2024年</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1348,7 +1345,7 @@
           <t>（对照）2025年</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1373,7 +1370,7 @@
           <t>2026年预测（中商产业研究院）</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1394,7 +1391,7 @@
           <t>2026年预测（摩根士丹利）</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1419,7 +1416,7 @@
           <t>（参考）2026年上半年实际</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="3" t="n">
         <v>4</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1439,7 +1436,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>数据来源：新战略咨询与人形机器人场景应用联盟《2025—2026年度人形机器人产业发展研究报告》（2026-03-30）、高工机器人GGII、中商产业研究院、摩根士丹利、新华网转引工业和信息化主管部门数据。</t>
         </is>
@@ -1477,7 +1474,7 @@
           <t>0~100万元</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="3" t="n">
         <v>54</v>
       </c>
       <c r="C48" s="3" t="inlineStr"/>
@@ -1494,7 +1491,7 @@
           <t>100万~1,000万元</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="3" t="n">
         <v>33</v>
       </c>
       <c r="C49" s="3" t="inlineStr"/>
@@ -1511,7 +1508,7 @@
           <t>1,000万元以上</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
@@ -1528,7 +1525,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="C51" s="3" t="inlineStr"/>
@@ -1536,7 +1533,7 @@
       <c r="E51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>数据来源：高工机器人（GGII）2025年人形机器人投招标统计。</t>
         </is>
@@ -1578,10 +1575,10 @@
           <t>宇树科技</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="3" t="n">
         <v>5500</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="3" t="n">
         <v>32.4</v>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1597,10 +1594,10 @@
           <t>智元机器人</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1616,10 +1613,10 @@
           <t>乐聚智能</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1635,10 +1632,10 @@
           <t>加速进化</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1654,10 +1651,10 @@
           <t>松延动力</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -1673,10 +1670,10 @@
           <t>其他厂商</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="3" t="n">
         <v>4500</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1692,10 +1689,10 @@
           <t>合计（全球）</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="3" t="n">
         <v>100</v>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1706,7 +1703,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>数据来源：北京赛迪出版传媒与中国电子报《2025年人形机器人市场研究报告》。优必选2025年年报披露全尺寸人形机器人销量1,079台，与第三方400—1,000台区间存在口径差异；新战略咨询口径下智元为5,168台、宇树与智元份额分别为25%和24%。</t>
         </is>
@@ -1744,7 +1741,7 @@
           <t>2023年（首台样机）</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C67" s="3" t="inlineStr"/>
@@ -1761,7 +1758,7 @@
           <t>2025年12月8日</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="3" t="n">
         <v>5000</v>
       </c>
       <c r="C68" s="3" t="inlineStr"/>
@@ -1778,7 +1775,7 @@
           <t>2026年3月30日</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="C69" s="3" t="inlineStr"/>
@@ -1795,7 +1792,7 @@
           <t>2026年6月28日</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="3" t="n">
         <v>15000</v>
       </c>
       <c r="C70" s="3" t="inlineStr"/>
@@ -1807,7 +1804,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>数据来源：智元机器人公开披露及媒体报道。</t>
         </is>
@@ -1845,7 +1842,7 @@
           <t>已保荐上市</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -1866,7 +1863,7 @@
           <t>正在保荐/在审/辅导</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -1887,7 +1884,7 @@
           <t>曾保荐但终止</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -1908,7 +1905,7 @@
           <t>股权投资参股</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -1929,7 +1926,7 @@
           <t>产业基金覆盖</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="3" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -1945,9 +1942,9 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>数据来源：本报告基于表12至表15统计。前四项单位为家、末项为只；产业基金多为综合性股权投资基金，机器人仅为其投资方向之一。</t>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：本报告基于表13至表16统计。前四项单位为家、末项为只；产业基金多为综合性股权投资基金，机器人仅为其投资方向之一。</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2016,7 @@
           <t>中国人形机器人出货量</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2044,7 +2041,7 @@
           <t>中国人形机器人出货量同比增速</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="3" t="n">
         <v>614.29</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2096,7 +2093,7 @@
           <t>中国人形机器人广义市场规模（含软件集成与服务）</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="3" t="n">
         <v>90</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2121,7 +2118,7 @@
           <t>中国人形机器人出货量（对照口径）</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2146,7 +2143,7 @@
           <t>全球人形机器人出货量</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2171,7 +2168,7 @@
           <t>中国企业出货量</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="3" t="n">
         <v>1.44</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2196,7 +2193,7 @@
           <t>中国企业占全球出货比重</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="3" t="n">
         <v>84.7</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2221,7 +2218,7 @@
           <t>全球前六名中国企业合计份额</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="3" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2246,7 +2243,7 @@
           <t>中国人形机器人出货量预测</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2271,7 +2268,7 @@
           <t>中国人形机器人销量预测</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2350,7 +2347,7 @@
           <t>中国人形机器人市场规模预测</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="3" t="n">
         <v>8700</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2375,7 +2372,7 @@
           <t>全球人形机器人出货量预测</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="3" t="n">
         <v>140</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2400,7 +2397,7 @@
           <t>全球人形机器人出货量（对照）</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2474,7 +2471,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>注：不同机构口径不一致，"中国出货2万台"与"全球出货1.7万台"来自不同统计体系，不可直接比较。</t>
         </is>
@@ -2689,7 +2686,7 @@
           <t>公开披露中标项目数量</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="3" t="n">
         <v>292</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2714,7 +2711,7 @@
           <t>披露合同金额合计</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2739,7 +2736,7 @@
           <t>0~100万元项目占比</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="3" t="n">
         <v>54</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2764,7 +2761,7 @@
           <t>100万~1,000万元项目占比</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="3" t="n">
         <v>33</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2789,7 +2786,7 @@
           <t>1,000万元以上项目占比</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2814,7 +2811,7 @@
           <t>亿元级项目数量</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2839,7 +2836,7 @@
           <t>优必选年度订单金额</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="3" t="n">
         <v>14</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2864,7 +2861,7 @@
           <t>优必选单笔最大采购合同</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2889,7 +2886,7 @@
           <t>优必选惠阳区数据采集中心中标金额</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="3" t="n">
         <v>5962.015</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2914,7 +2911,7 @@
           <t>优必选与天奇股份Walker S2采购订单</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="3" t="n">
         <v>3000</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2939,7 +2936,7 @@
           <t>松延动力全年总订单</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="3" t="n">
         <v>2500</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2964,7 +2961,7 @@
           <t>松延动力合同总额</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2989,7 +2986,7 @@
           <t>众擎与多伦科技框架采购协议</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3014,7 +3011,7 @@
           <t>星动纪元总订单</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3181,7 +3178,7 @@
           <t>国产17系列谐波减速器价格较进口下降</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="3" t="n">
         <v>45</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3233,7 +3230,7 @@
           <t>供应链响应速度较2023年提升</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="3" t="n">
         <v>60</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3285,7 +3282,7 @@
           <t>来福谐波谐波减速器平均售价</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="3" t="n">
         <v>795</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3310,7 +3307,7 @@
           <t>来福谐波谐波减速器平均售价</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="3" t="n">
         <v>571</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3335,7 +3332,7 @@
           <t>轮式人形机器人整机成本</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3360,7 +3357,7 @@
           <t>—其中轮式底盘</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -3385,7 +3382,7 @@
           <t>—其中协作臂</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -3410,7 +3407,7 @@
           <t>—其中灵巧手</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -3551,7 +3548,7 @@
           <t>中国谐波减速器市场规模</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="3" t="n">
         <v>19.09</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3576,7 +3573,7 @@
           <t>中国谐波减速器市场规模</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="3" t="n">
         <v>51.53</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3601,7 +3598,7 @@
           <t>2019—2023年复合增长率</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="3" t="n">
         <v>28.18</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3626,7 +3623,7 @@
           <t>中国谐波减速器销量</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="3" t="n">
         <v>119</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3678,7 +3675,7 @@
           <t>绿的谐波中国市占率</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="3" t="n">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3703,7 +3700,7 @@
           <t>来福谐波中国市占率</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3728,7 +3725,7 @@
           <t>TOP4合计市场份额</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="3" t="n">
         <v>64.13</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3753,7 +3750,7 @@
           <t>TOP4份额较2023年提升</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="3" t="n">
         <v>4.77</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3778,7 +3775,7 @@
           <t>工业机器人用谐波减速器国产化率</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="3" t="n">
         <v>30</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3803,7 +3800,7 @@
           <t>国产化率预期</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="3" t="n">
         <v>40</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -4024,7 +4021,7 @@
           <t>步科股份无框力矩电机销量</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4049,7 +4046,7 @@
           <t>步科股份无框力矩电机销量</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4189,7 +4186,7 @@
           <t>其中内资企业数量</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4241,7 +4238,7 @@
           <t>特斯拉Optimus单台编码器用量</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="3" t="n">
         <v>54</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4354,7 +4351,7 @@
           <t>全球关节模组需求量</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="3" t="n">
         <v>72</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4379,7 +4376,7 @@
           <t>其中国产人形整机需求占比</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="3" t="n">
         <v>70</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -4485,7 +4482,7 @@
           <t>Optimus Gen2整机硬件成本</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4510,7 +4507,7 @@
           <t>—其中28个一体化关节模组占比</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="3" t="n">
         <v>54</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4650,7 +4647,7 @@
           <t>Optimus单台行星滚柱丝杠用量</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="3" t="n">
         <v>14</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -4675,7 +4672,7 @@
           <t>全球人形机器人用行星滚柱丝杠收入规模</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4700,7 +4697,7 @@
           <t>灵巧手占整机成本</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -4725,7 +4722,7 @@
           <t>全球人形机器人灵巧手市场规模</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="3" t="n">
         <v>71</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -4750,7 +4747,7 @@
           <t>全球人形机器人灵巧手市场规模</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="3" t="n">
         <v>419</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -4775,7 +4772,7 @@
           <t>宇树Dex5灵巧手自由度</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4800,7 +4797,7 @@
           <t>宇树Dex5触觉传感器数量</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="3" t="n">
         <v>94</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4852,7 +4849,7 @@
           <t>中国六维力传感器市场规模</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="3" t="n">
         <v>3.88</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4904,7 +4901,7 @@
           <t>计算与感知占整机成本</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4934,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4948,7 +4945,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>整机制造环节代表性企业数据（对应报告第5章、表7）</t>
+          <t>整机制造环节代表性企业数据（对应报告第5章、表7—表8）</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5085,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>注：智元、优必选与第三方统计口径存在差异，第4.1节份额图采用第三方统一口径。</t>
         </is>
@@ -5097,7 +5094,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>4.2 第二梯队与新兴整机企业（对应报告表7）</t>
+          <t>4.2 第二梯队与新兴整机企业（对应报告表8）</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5730,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>注：特斯拉产能规划历史上多次延期，上述目标为方向性参考。</t>
         </is>
@@ -5742,24 +5739,36 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>4.4 智元机器人专项（对应报告5.2节、图7）</t>
+          <t>4.4 智元机器人产品线（对应报告表7）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>维度</t>
+          <t>产品系列</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>代表机型</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>形态与关键参数</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>公开定价</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>主要应用场景</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>来源</t>
@@ -5769,192 +5778,206 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>公司沿革</t>
+          <t>远征系列</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>成立于2023年2月，由彭志辉（稚晖君）与邓泰华共同创立；现定位为"具身智能基础模型公司"</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
+          <t>远征A1、远征A2</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>全尺寸双足人形；A2具备10余种微表情、100余种拟人动作、360°自主行走避障，可完成太极/打鼓/京剧/电吉他等数十种表演；曾完成百公里跨省行走</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>远征A2青春版16.8万元</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>工业搬运、巡检、导览、展厅讲解、贵宾服务、文娱表演</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>公司公开披露</t>
+          <t>公司官网及发布信息</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>产品线—远征系列</t>
+          <t>灵犀系列（双足）</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>A1/A2，全尺寸双足，强调长距离行走与复杂环境适应，面向工业搬运、巡检、导览、展示；2024年8月发布远征A2并进入商用交付</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
+          <t>灵犀X1、灵犀X2</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>半尺寸双足人形，X2身高约1.31米；青春版27自由度仿生关节、30余种微表情、20种预设动作库；探索版31自由度模块化架构，支持末端执行器与感知交互器件更换</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>灵犀X2青春版9.8万元</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>文娱商演、科研教育、门店服务</t>
+        </is>
+      </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>公司公开披露</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>产品线—灵犀系列</t>
+          <t>灵犀系列（四足/其他）</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>X1/X2及D1 Ultra／Pro，覆盖人形、轮式与臂台一体设备；X2身高约1.3米；面向仓储、制造、服务场景的操作与搬取</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
+          <t>D1 Pro、D1 EDU、D1 Ultra</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>强化学习运控算法；连续攀爬16cm台阶；续航1—2小时</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>巡检、科研教育、复杂地形作业</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>公司公开披露</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>产品线—精灵系列</t>
+          <t>精灵系列</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>G1/G2，中小型轮式双臂，偏向开发、教学与实验验证，作为高校与企业的具身平台</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>精灵G1、精灵G2</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>轮式双臂机型，以轮式底盘换取稳定性、续航与成本优势</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>精灵G1售价45万元</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>工业物流、商用服务、高校与企业具身智能开发教学平台</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>公司公开披露</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>操作系统</t>
+          <t>（出货结构）</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>灵渠OS，原生适配具身智能的开源操作系统</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>截至2025/12/8累计5,000台</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>灵犀系列1,846台、远征系列1,742台、精灵系列1,412台</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>三线出货较为均衡</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>公司公开披露</t>
+          <t>公司披露</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>基座模型</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>启元大模型GenieOperator-1，2026年3月10日发布，融合多模态大模型与混合专家系统</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>公司公开披露</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>战略规划</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026年进入"部署态"阶段，推出AIMA全栈生态开发平台，全面开放"1+3+X"架构</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>公司公开披露</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>说明：2025年8月18日全系产品正式开售。定价为公开披露的对外售价，实际成交价可能因配置与批量而异。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>生态投入</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>"元苼生态计划"，未来五年投入20多亿元，扶持科研学术、教育人才、生态伙伴与开发者社区</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>公司公开披露</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>供应链体系</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>建立"全球首个具身智能机器人标准化供应链体系"（A链），覆盖上下游全环节；量产依托上海本地"半小时供应链"</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>公开报道</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4.5 智元机器人专项（对应报告5.2节、图7）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>订单与产能</t>
+          <t>公司沿革</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>年度订单需求超10万台，对应规划产能达10万台级；有报道指1.5万台量产背后产业链已出现承压</t>
+          <t>成立于2023年2月，由彭志辉（稚晖君）与邓泰华共同创立；现定位为"具身智能基础模型公司"</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
@@ -5962,19 +5985,19 @@
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>公开报道</t>
+          <t>公司公开披露</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>资本化—A股平台</t>
+          <t>产品线—远征系列</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>2025/7/8受让上纬新材29.99%；9/23完成过户；"协议转让＋部分要约"合计21亿元取得控股权，智元恒岳及一致行动人合计持股63.62%</t>
+          <t>A1/A2，全尺寸双足，强调长距离行走与复杂环境适应，面向工业搬运、巡检、导览、展示；2024年8月发布远征A2并进入商用交付</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr"/>
@@ -5982,19 +6005,19 @@
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>上纬新材公告</t>
+          <t>公司公开披露</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>资本化—港股IPO</t>
+          <t>产品线—灵犀系列</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026/7/24正式启动赴港上市流程，中金公司＋中信证券＋摩根士丹利承销；投资人称目标估值400亿—500亿港元</t>
+          <t>X1/X2及D1 Ultra／Pro，覆盖人形、轮式与臂台一体设备；X2身高约1.3米；面向仓储、制造、服务场景的操作与搬取</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr"/>
@@ -6002,19 +6025,19 @@
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>公开报道</t>
+          <t>公司公开披露</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>与国泰海通的关系</t>
+          <t>产品线—精灵系列</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>国泰君安创新投资曾参投智元机器人融资</t>
+          <t>G1/G2，中小型轮式双臂，偏向开发、教学与实验验证，作为高校与企业的具身平台</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr"/>
@@ -6022,12 +6045,432 @@
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>灵渠OS，原生适配具身智能的开源操作系统</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>基座模型</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>启元大模型GenieOperator-1，2026年3月10日发布，融合多模态大模型与混合专家系统</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>战略规划</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2026年进入"部署态"阶段，推出AIMA全栈生态开发平台，全面开放"1+3+X"架构</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>生态投入</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>"元苼生态计划"，未来五年投入20多亿元，扶持科研学术、教育人才、生态伙伴与开发者社区</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>公司公开披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>供应链体系</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>建立"全球首个具身智能机器人标准化供应链体系"（A链），覆盖上下游全环节；量产依托上海本地"半小时供应链"</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>订单与产能</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>年度订单需求超10万台，对应规划产能达10万台级；有报道指1.5万台量产背后产业链已出现承压</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>资本化—A股平台</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2025/7/8受让上纬新材29.99%；9/23完成过户；"协议转让＋部分要约"合计21亿元取得控股权，智元恒岳及一致行动人合计持股63.62%</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>上纬新材公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>资本化—港股IPO</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>2026/7/24正式启动赴港上市流程，中金公司＋中信证券＋摩根士丹利承销；投资人称目标估值400亿—500亿港元</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>创始团队</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>邓泰华：创始人/董事长/CEO，华为二十余年、曾任计算产品线总裁，统筹战略、资本运作与AI生态；彭志辉（稚晖君）：联合创始人/总裁/CTO，2020年加入华为从事昇腾AI芯片与AI算法研究，主攻机器人全栈研发；姜青松负责ToB运营，姚卯青负责智能驾驶级业务落地</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>公司披露、公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>组织模式</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>较明显借鉴华为模式：分工规范严谨，员工手册详细明确且公开；核心管理层9人中华为背景占5席</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>研发双套机制</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>机制一：数十人规模的"创新团队"，不设OKR/KPI、不背商业化目标，专注0到1探索；机制二：Genie、通用、灵犀等大部分团队，专注1到N落地与规模化交付。另设平台管理部（技术中台），研发软硬件基础能力并复用至各产品线</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>供应链—A链核心伙伴</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>宁波华翔、立讯精密、博众精工、领益智造、蓝思科技、卧龙电驱、均普智能</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>供应链—关键零部件</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>谐波减速器：绿的谐波；行星减速器：中大力德；关节模组：富临精工；3D视觉传感器：奥比中光；IMU：华依科技</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>供应链—代工</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>均普智能（本体代工）、蓝思科技（灵犀X1代工）、宁波华翔（本体代工支持）</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>供应链—新增厂商</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2025下半年至2026年新增：雷赛智能、江苏雷利、龙溪股份、威孚高科、鸣志电器、爱仕达、沪光股份等</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>供应链绑定模式</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>"投资＋入股＋采购"三重绑定：接受投资的供应商同时成为股东与客户；成立不到三年投资近30家公司、设立17家合资公司；2025年6月与地方国资及Hope Robotics成立浙江杭绍具身智能技术创新公司并持股30%；并成为高瓴LP</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>融资历程</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2023年完成5轮；2024年完成2轮；2025年3月腾讯投资领投（腾讯首次进入具身智能），5月新增京东与上海具身智能基金，红杉中国、TCL创投、沃赋创投、尚颀资本等跟投；截至2025年8月累计11轮、融资超30亿元</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>股东阵容</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>财务投资人：高瓴、蓝驰创投、中科创星、沃赋创投、奇绩创坛等；产业股东：上汽、比亚迪、京东、腾讯、三花控股等；国际投资人：正大集团、韩国LG电子、韩国未来资产等；股改后马化腾、王传福位列股东</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>估值轨迹（口径不一，须谨慎引用）</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2024年底A轮阶段超70亿元；2025年5月B+轮后150亿元；2025年11月最新一轮约520亿元；2026年7月赴港目标估值400亿—500亿港元（约363亿—455亿元），另有传闻按约200亿美元推进。各数字时点与币种口径混用且不自洽</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>公开报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>生态投入</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>"元苼生态计划"，未来五年投入20多亿元，扶持科研学术、教育人才、生态伙伴与开发者社区；对外表达"饱和式投入、不闭门造机器人"</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>公司披露</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>与国泰海通的关系</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资曾参投智元机器人融资</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
           <t>Wind整理成果</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>说明：本工作表新增，对应报告第5.2节的智元机器人专项分析与图7。</t>
         </is>
@@ -6058,14 +6501,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人形机器人产业链企业资本化进度（对应报告第6章、表8—表10）</t>
+          <t>人形机器人产业链企业资本化进度（对应报告第6章、表9—表11）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>5.1 已上市或已完成发行（对应表8）</t>
+          <t>5.1 已上市或已完成发行（对应表9）</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6897,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件；各公司年报及公告。本报告复核后补充三瑞智能、兆威机电、来福谐波，并订正绿的谐波、步科股份的保荐机构归属。</t>
         </is>
@@ -6463,7 +6906,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>5.2 在审、已受理或已递表（对应表9）</t>
+          <t>5.2 在审、已受理或已递表（对应表10）</t>
         </is>
       </c>
     </row>
@@ -6692,7 +7135,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
         </is>
@@ -6701,7 +7144,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>5.3 辅导备案或已完成股改（对应表10）</t>
+          <t>5.3 辅导备案或已完成股改（对应表11）</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7533,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；公开融资报道。本报告复核后订正首形科技的主营业务及A2轮跟投主体。</t>
         </is>
@@ -7200,7 +7643,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>数据来源：上纬新材公告；上交所审核信息；公开报道。</t>
         </is>
@@ -7283,7 +7726,7 @@
           <t>中国人形机器人产业股权融资额</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="3" t="n">
         <v>889</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -7345,7 +7788,7 @@
           <t>具身智能百亿估值独角兽数量</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="3" t="n">
         <v>13</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -7458,14 +7901,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表11—表15）</t>
+          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表12—表16）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>6.1 券商谱系（对应表11）</t>
+          <t>6.1 券商谱系（对应表12）</t>
         </is>
       </c>
     </row>
@@ -7590,7 +8033,7 @@
       <c r="F9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>资料来源：各券商公开披露。国泰证券与君安证券的存续期远早于人形机器人产业兴起，本表所列关联均发生于国泰君安、海通证券及国泰海通期间。</t>
         </is>
@@ -7750,7 +8193,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>6.3 已保荐上市（对应表12）</t>
+          <t>6.3 已保荐上市（对应表13）</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8486,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
         </is>
@@ -8052,7 +8495,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>6.4 正在保荐、在审或辅导（对应表13）</t>
+          <t>6.4 正在保荐、在审或辅导（对应表14）</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8724,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
         </is>
@@ -8361,7 +8804,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>6.6 股权投资参股（对应表14）</t>
+          <t>6.6 股权投资参股（对应表15）</t>
         </is>
       </c>
     </row>
@@ -8622,7 +9065,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
         </is>
@@ -8631,7 +9074,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>6.7 产业基金布局（对应表15）</t>
+          <t>6.7 产业基金布局（对应表16）</t>
         </is>
       </c>
     </row>
@@ -8892,7 +9335,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
         </is>
@@ -9008,7 +9451,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>无锡巨蟹智能驱动科技有限公司相关数据（对应报告第8章）</t>
+          <t>无锡巨蟹智能驱动科技有限公司相关数据（对应报告第8章、表17）</t>
         </is>
       </c>
     </row>
@@ -9701,7 +10144,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>注：无锡巨蟹为未上市公司，财务数据未公开披露，本表仅作定位对照，不构成估值依据。</t>
         </is>
@@ -10442,7 +10885,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>说明：因外部网络访问受限，本报告数据以可公开检索到的资料内容为准；涉及未上市企业的经营与估值数据均来自公开报道，未经审计核验，使用时请以最新公开披露为准。</t>
         </is>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -2480,29 +2480,29 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2.2 2025年中国人形机器人五大应用场景（对应报告表6）</t>
+          <t>2.2 下游应用场景的两套分类与规模参考（对应报告表6）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>应用场景</t>
+          <t>三分类（企业口径）</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>主要采购方</t>
+          <t>对应的五分类场景</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>采购规模特征</t>
+          <t>采购主体与特征</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>单价水平</t>
+          <t>规模/占比参考</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2514,135 +2514,115 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>教育科研</t>
+          <t>科研教育</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>高校、职业院校及科研机构</t>
+          <t>教育科研、数据采集</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>采购频次高、单次规模小；出货量大而市场规模小</t>
+          <t>高校、职业院校、科研机构，政务平台与国资产业基地；教育科研频次高单次小、单价几万至一二十万元；数据采集单次常在百台以上、服务占比高</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>几万元至一二十万元</t>
+          <t>宇树2025年前三季度人形机器人收入中科研教育占73.6%；数据采集为2025年千万元级与亿元级订单主要来源</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>高工机器人GGII</t>
+          <t>宇树招股文件；新战略咨询/人形机器人场景应用联盟</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>数据采集</t>
+          <t>商业消费</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>政务平台与国资产业基地</t>
+          <t>交互服务、娱乐表演</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>单次采购一般在百台以上，服务占比高</t>
+          <t>企业展厅、博物馆、文旅场所、租赁与商演公司；对可靠性与外观要求高、对负载要求低，需求弹性大</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>较高</t>
+          <t>宇树四足机器人商业消费领域收入增速明显高于科研教育；人形机器人该类占比未单独披露</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>高工机器人GGII</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>交互服务</t>
+          <t>行业应用</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>企业展厅、博物馆及文旅场所</t>
+          <t>工业物流</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>以展示导览为主，对负载要求低</t>
+          <t>大型制造与物流企业，智能巡检、消防应急等特种作业主体；单价最高、服务占比高，仍处试点</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>宇树2025年前三季度人形机器人收入中工业商用约9%；定制开发产品占比1.71%</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>高工机器人GGII</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>工业物流</t>
+          <t>（参考）宇树收入结构</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大型制造与物流企业</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>仍处试点阶段，规模较小，服务占比高</t>
+          <t>四足机器人收入占比 76.57%→75.78%→59.53%→42.25%；人形机器人收入占比 0%→1.88%→27.60%→51.53%</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>最高</t>
+          <t>报告期各期，人形占比快速提升</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>高工机器人GGII</t>
+          <t>宇树科技招股文件</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>娱乐表演</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>租赁及商演公司</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>短周期租赁与活动，需求波动大</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>中低</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>高工机器人GGII</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>说明：目前尚无机构按统一口径披露全行业各场景的出货量或市场规模占比，占比数据为宇树单家公司口径，不代表全行业结构。</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4314,7 +4294,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.4 一体化关节模组环节</t>
+          <t>3.4 力/力矩传感器环节（对应报告表3；依批注由其他环节移入核心环节）</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4306,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>数值/内容</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4348,15 +4328,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>全球关节模组需求量</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>72</v>
+          <t>中国六维力传感器市场规模</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>&gt;3</t>
+        </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>万个</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -4366,103 +4348,101 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>其中国产人形整机需求占比</t>
+          <t>中国六维力传感器市场规模</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>70</v>
+        <v>3.88</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>2026年预测</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>全球头部整机企业合计规划产能</t>
+          <t>应变片技术市场份额</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>&gt;10</t>
+          <t>&gt;80</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>万台</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>当前</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>预计实际交付规模</t>
+          <t>MEMS方案体积</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>4~6</t>
+          <t>可降至传统产品的1/10</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>万台</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>在研</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>宇立仪器、坤维科技</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>关节模组占整机BOM成本</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>35~60</t>
-        </is>
+          <t>蓝点触控高维解耦模型训练样本</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>53</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>万个样本点</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -4472,22 +4452,24 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>公开报道</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Optimus Gen2整机硬件成本</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>29</v>
+          <t>坤维科技标定技术</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>六轴联合加载标定</t>
+        </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -4497,22 +4479,24 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>公开报道</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>—其中28个一体化关节模组占比</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>54</v>
+          <t>关节内置力矩传感器供给方式</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>多由关节模组厂商自研并随模组交付，独立外售规模有限</t>
+        </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -4522,24 +4506,24 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>本报告整理</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>—单套关节模组价格区间</t>
+          <t>代表企业—六维力传感器</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>4000~6500</t>
+          <t>坤维科技、宇立仪器、蓝点触控、柯力传感、安培龙</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -4549,19 +4533,19 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2030年头部企业数量与合计份额</t>
+          <t>代表企业—关节内置力矩传感器</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>5~8家占80%以上</t>
+          <t>无锡巨蟹、绿的谐波等关节模组厂商自研</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -4571,31 +4555,31 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>2030年预测</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>公开资料</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.5 其他上游环节（对应报告表5）</t>
+          <t>3.5 一体化关节模组环节</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>环节</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>关键数据</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4617,167 +4601,171 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>行星滚柱丝杠占整机BOM成本</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>近20</t>
-        </is>
+          <t>全球关节模组需求量</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>72</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>万个</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Optimus单台行星滚柱丝杠用量</t>
+          <t>其中国产人形整机需求占比</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>全球人形机器人用行星滚柱丝杠收入规模</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>30.1</v>
+          <t>全球头部整机企业合计规划产能</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>&gt;10</t>
+        </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>万台</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2026年</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>第三方研究</t>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>灵巧手占整机成本</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>15</v>
+          <t>预计实际交付规模</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>4~6</t>
+        </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>万台</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026年</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>全球人形机器人灵巧手市场规模</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>71</v>
+          <t>关节模组占整机BOM成本</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>35~60</t>
+        </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>全球人形机器人灵巧手市场规模</t>
+          <t>Optimus Gen2整机硬件成本</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>419</v>
+        <v>29</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>2030年预测</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>宇树Dex5灵巧手自由度</t>
+          <t>—其中28个一体化关节模组占比</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -4787,22 +4775,24 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>公司资料</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>宇树Dex5触觉传感器数量</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>94</v>
+          <t>—单套关节模组价格区间</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>4000~6500</t>
+        </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>元</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4812,111 +4802,302 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>公司资料</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>中国六维力传感器市场规模</t>
+          <t>2030年头部企业数量与合计份额</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>&gt;3</t>
+          <t>5~8家占80%以上</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>2030年预测</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>行业白皮书</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.6 其他上游环节（对应报告表5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>关键数据</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>年度/口径</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>行星滚柱丝杠占整机BOM成本</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>近20</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>行业测算</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Optimus单台行星滚柱丝杠用量</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>行业测算</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>全球人形机器人用行星滚柱丝杠收入规模</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>第三方研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>灵巧手占整机成本</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>行业测算</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>全球人形机器人灵巧手市场规模</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>行业研究</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>中国六维力传感器市场规模</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>全球人形机器人灵巧手市场规模</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>419</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>2026年预测</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2030年预测</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>行业研究</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>应变片技术市场份额</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>&gt;80</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>宇树Dex5灵巧手自由度</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>公司资料</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>宇树Dex5触觉传感器数量</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>公司资料</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>计算与感知占整机成本</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>当前</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>行业研究</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>计算与感知占整机成本</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>行业测算</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>说明：力/力矩传感器因与无锡巨蟹直接相关，已由本表移入"3.4 力/力矩传感器环节"。</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6940,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>工业机器人控制系统</t>
+          <t>工业机器人控制系统及部件、伺服系统及部件；产品含成套控制系统、驱控一体控制系统、控制系统单机，以及伺服驱动器、电机、编码器</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>国家级高新技术企业；受理到上市约12个月</t>
+          <t>全称临海市新睿电子科技股份有限公司（浙江台州临海）。2023—2025年营收2.04/3.01/3.18亿元，归母净利0.31/0.55/0.59亿元；控制系统销量3.87/6.78/8.44万套；专利58项（发明27项）、软著146项。伺服驱动器、电机、编码器与巨蟹自研部件重合</t>
         </is>
       </c>
     </row>
@@ -6791,12 +6972,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>无人机电动动力系统及机器人动力系统（电机、模组）</t>
+          <t>无人机电动动力系统（电机、电子调速器、螺旋桨、一体化动力系统，60余系列400余款）及机器人动力系统（电机、模组），并布局eVTOL动力系统</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>发行4,001万股；按2024年销售额计全球民用无人机电动动力系统份额7.1%、第二</t>
+          <t>全称南昌三瑞智能科技股份有限公司，成立于2009年。据弗若斯特沙利文为全球最大独立第三方民用无人机动力系统供应商，2024年全球份额7.1%、第二。应用于农林植保、工业巡检、测绘、物流、应急救援、安防、航模与灯光秀。发行4,001万股。机器人动力系统与巨蟹环节部分重合</t>
         </is>
       </c>
     </row>
@@ -7252,12 +7433,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>完成E轮融资与股改，已启动科创板辅导准备</t>
+          <t>完成E轮融资与股改，已启动科创板辅导准备与申报</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7289,7 +7470,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露（拟境外上市）</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7316,12 +7497,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>已完成股改，最新一轮视为Pre-IPO轮</t>
+          <t>已完成股改，最新一轮视为Pre-IPO轮，计划2026年四季度上市</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7353,7 +7534,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -7385,7 +7566,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -7417,7 +7598,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -7449,7 +7630,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -7481,7 +7662,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -7513,7 +7694,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -7535,7 +7716,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；公开融资报道。本报告复核后订正首形科技的主营业务及A2轮跟投主体。</t>
+          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；公开融资报道。辅导机构一栏仅纽氏达特与天链机器人已完成辅导备案并公示；其余企业仅完成股改、尚未提交辅导备案，故未公开披露，本报告不作推测。本报告复核后订正首形科技的主营业务及A2轮跟投主体。</t>
         </is>
       </c>
     </row>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>报告图1—图8制图数据</t>
+          <t>报告图1—图9制图数据</t>
         </is>
       </c>
     </row>
@@ -1233,31 +1233,23 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>图4  中国人形机器人出货量：历史实际与2026年预测（柱状图）</t>
+          <t>图4  2025年中国人形机器人出货量的应用场景结构（饼图）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>年度/情景</t>
+          <t>应用场景</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>出货量(万台)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>数据性质</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>来源机构</t>
-        </is>
-      </c>
+          <t>出货量占比(%)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>备注</t>
@@ -1267,201 +1259,155 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>教育科研</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>实际（倒算）</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>新战略咨询/人形机器人场景应用联盟</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>按该报告披露2025年2万台、同比+614.29%倒算</t>
+          <t>出货量占比最高、单价最低；采购方为高校、职业院校与科研机构</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>数据采集</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>实际</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>新战略咨询/人形机器人场景应用联盟</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>整机市场规模约50亿—65亿元，广义市场规模约90亿元</t>
+          <t>单次采购常在百台以上、服务占比高；采购方为政务平台与国资产业基地</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>（对照）2024年</t>
+          <t>交互服务</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>实际</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>高工机器人GGII</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>GGII口径较严，须完成交付验收并能实际运行</t>
+          <t>企业展厅、博物馆及文旅场所</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>（对照）2025年</t>
+          <t>娱乐表演</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>实际</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>高工机器人GGII</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>同比增长超650%</t>
+          <t>租赁与商演公司，需求弹性大</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026年预测（中商产业研究院）</t>
+          <t>工业物流</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>预测</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>中商产业研究院</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>轧差项＝100%－上述四项；单价最高但仍处试点</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026年预测（摩根士丹利）</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>预测</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>摩根士丹利</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>较2025年翻倍增长</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>（参考）2026年上半年实际</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>实际</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>工业和信息化主管部门</t>
-        </is>
-      </c>
+          <t>（市场规模口径）</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>数据采集、教育科研、交互服务三者合计超80%</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>上半年出货已超4万台，全年产量有望冲刺10万台</t>
+          <t>同一报告披露，未给出各场景的单项规模占比</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>数据来源：新战略咨询与人形机器人场景应用联盟《2025—2026年度人形机器人产业发展研究报告》（2026-03-30）、高工机器人GGII、中商产业研究院、摩根士丹利、新华网转引工业和信息化主管部门数据。</t>
+          <t>数据来源：新战略咨询与人形机器人场景应用联盟《2025—2026年度人形机器人产业发展研究报告》，2026年3月30日发布。前四项为该报告披露值，工业物流为轧差值。与本工作簿2.1节的2万台出货量为同一来源、同一口径。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>图5  2025年中国人形机器人中标项目金额分布（条形图）</t>
+          <t>图5  中国人形机器人出货量：历史实际与2026年预测（柱状图）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>金额区间</t>
+          <t>年度/情景</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>项目数量占比(%)</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>出货量(万台)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>数据性质</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>来源机构</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>备注</t>
@@ -1471,263 +1417,301 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>0~100万元</t>
+          <t>2024年</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>实际（倒算）</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>新战略咨询/人形机器人场景应用联盟</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>全年公开披露中标项目292个</t>
+          <t>按该报告披露2025年2万台、同比+614.29%倒算</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>100万~1,000万元</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>新战略咨询/人形机器人场景应用联盟</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>披露合同金额合计超18.1亿元</t>
+          <t>整机市场规模约50亿—65亿元，广义市场规模约90亿元</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1,000万元以上</t>
+          <t>（对照）2024年</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C50" s="3" t="inlineStr"/>
-      <c r="D50" s="3" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>高工机器人GGII</t>
+        </is>
+      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>其中亿元级项目10个</t>
+          <t>GGII口径较严，须完成交付验收并能实际运行</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>（对照）2025年</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>高工机器人GGII</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>同比增长超650%</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：高工机器人（GGII）2025年人形机器人投招标统计。</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026年预测（中商产业研究院）</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>预测</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>中商产业研究院</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026年预测（摩根士丹利）</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>预测</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>摩根士丹利</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>较2025年翻倍增长</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>图6  2025年全球人形机器人出货量企业份额（饼图）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>出货量(台)</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>份额(%)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>（参考）2026年上半年实际</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>工业和信息化主管部门</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>上半年出货已超4万台，全年产量有望冲刺10万台</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：新战略咨询与人形机器人场景应用联盟《2025—2026年度人形机器人产业发展研究报告》（2026-03-30）、高工机器人GGII、中商产业研究院、摩根士丹利、新华网转引工业和信息化主管部门数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>图6  2025年中国人形机器人中标项目金额分布（条形图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>金额区间</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>项目数量占比(%)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>宇树科技</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>出货量与份额均居全球第一，纯人形口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>公司自主披露截至2025/12/8累计交付5,000台</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>乐聚智能</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>并列第三</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>加速进化</t>
+          <t>0~100万元</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>5.9</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>并列第三</t>
+          <t>全年公开披露中标项目292个</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>松延动力</t>
+          <t>100万~1,000万元</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>5.9</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>并列第三</t>
+          <t>披露合同金额合计超18.1亿元</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>其他厂商</t>
+          <t>1,000万元以上</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>26.5</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>轧差项</t>
+          <t>其中亿元级项目10个</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>合计（全球）</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="C62" s="3" t="n">
         <v>100</v>
       </c>
+      <c r="C62" s="3" t="inlineStr"/>
       <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>中国企业合计约1.44万台，占84.7%</t>
-        </is>
-      </c>
+      <c r="E62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>数据来源：北京赛迪出版传媒与中国电子报《2025年人形机器人市场研究报告》。优必选2025年年报披露全尺寸人形机器人销量1,079台，与第三方400—1,000台区间存在口径差异；新战略咨询口径下智元为5,168台、宇树与智元份额分别为25%和24%。</t>
+          <t>数据来源：高工机器人（GGII）2025年人形机器人投招标统计。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>图7  智元机器人累计量产下线台数（柱状图）</t>
+          <t>图7  2025年全球人形机器人出货量企业份额（饼图）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>企业</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>累计下线台数(台)</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+          <t>出货量(台)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>份额(%)</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -1738,211 +1722,377 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2023年（首台样机）</t>
+          <t>宇树科技</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C67" s="3" t="inlineStr"/>
+        <v>5500</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>32.4</v>
+      </c>
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>公司披露的初期样机数量，与后续累计量产口径不完全一致</t>
+          <t>出货量与份额均居全球第一，纯人形口径</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2025年12月8日</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C68" s="3" t="inlineStr"/>
+        <v>4000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>灵犀X1/X2 1,846台、远征A1/A2 1,742台、精灵G1/G2 1,412台</t>
+          <t>公司自主披露截至2025/12/8累计交付5,000台</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026年3月30日</t>
+          <t>乐聚智能</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C69" s="3" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5.9</v>
+      </c>
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>突破万台</t>
+          <t>并列第三</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026年6月28日</t>
+          <t>加速进化</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C70" s="3" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>5.9</v>
+      </c>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>半年内由1万台增至1.5万台</t>
+          <t>并列第三</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：智元机器人公开披露及媒体报道。</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>松延动力</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>并列第三</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>其他厂商</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>轧差项</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>图8  国泰海通系与人形机器人产业链公司的关联分布（条形图）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>关联类型</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>公司/基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>已保荐上市</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>绿的谐波、步科股份、优必选、越疆科技(港)、三瑞智能、乐动机器人、新睿电子、珞石机器人</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>合计（全球）</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>中国企业合计约1.44万台，占84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：北京赛迪出版传媒与中国电子报《2025年人形机器人市场研究报告》。优必选2025年年报披露全尺寸人形机器人销量1,079台，与第三方400—1,000台区间存在口径差异；新战略咨询口径下智元为5,168台、宇树与智元份额分别为25%和24%。</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>正在保荐/在审/辅导</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>越疆科技(A股)、卡诺普机器人、卧安机器人、晋拓股份(定增)、智谱(辅导)、镭神技术(辅导)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>曾保荐但终止</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>节卡股份</t>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>图8  智元机器人累计量产下线台数（柱状图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>累计下线台数(台)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>股权投资参股</t>
+          <t>2023年（首台样机）</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
       <c r="D78" s="3" t="inlineStr"/>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>智元机器人、智平方、首形科技、宇树科技、银河通用(间接)、飒智智能、某协作机器人企业</t>
+          <t>公司披露的初期样机数量，与后续累计量产口径不完全一致</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>产业基金覆盖</t>
+          <t>2025年12月8日</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr"/>
       <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
+          <t>灵犀X1/X2 1,846台、远征A1/A2 1,742台、精灵G1/G2 1,412台</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026年3月30日</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>突破万台</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026年6月28日</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>半年内由1万台增至1.5万台</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：智元机器人公开披露及媒体报道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>图9  国泰海通系与人形机器人产业链公司的关联分布（条形图）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>关联类型</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>公司/基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>已保荐上市</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>绿的谐波、步科股份、优必选、越疆科技(港)、三瑞智能、乐动机器人、新睿电子、珞石机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>正在保荐/在审/辅导</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>越疆科技(A股)、卡诺普机器人、卧安机器人、晋拓股份(定增)、智谱(辅导)、镭神技术(辅导)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>曾保荐但终止</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>节卡股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>股权投资参股</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>智元机器人、智平方、首形科技、宇树科技、银河通用(间接)、飒智智能、某协作机器人企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>产业基金覆盖</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>只</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
           <t>中际旭创产业基金、江城神工基金、科创主题基金矩阵、恒旭资本第四期、上海AI母基金、海通中小企业发展基金、浦东引领区海通母基金等</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>数据来源：本报告基于表13至表16统计。前四项单位为家、末项为只；产业基金多为综合性股权投资基金，机器人仅为其投资方向之一。</t>
         </is>
@@ -2480,7 +2630,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2.2 下游应用场景的两套分类与规模参考（对应报告表6）</t>
+          <t>2.2 下游应用场景结构（对应报告表6、图4）</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2647,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>出货量占比</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>采购主体与特征</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>规模/占比参考</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>市场规模口径下的地位</t>
         </is>
       </c>
     </row>
@@ -2524,17 +2674,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>合计61%（教育科研42%＋数据采集19%）</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
           <t>高校、职业院校、科研机构，政务平台与国资产业基地；教育科研频次高单次小、单价几万至一二十万元；数据采集单次常在百台以上、服务占比高</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>宇树2025年前三季度人形机器人收入中科研教育占73.6%；数据采集为2025年千万元级与亿元级订单主要来源</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>宇树招股文件；新战略咨询/人形机器人场景应用联盟</t>
+          <t>两者均属规模最大的三个场景；数据采集为2025年千万元级与亿元级订单主要来源。参照：宇树2025年前三季度人形机器人收入中科研教育占73.6%</t>
         </is>
       </c>
     </row>
@@ -2551,17 +2701,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>合计35%（交互服务19%＋娱乐表演16%）</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>企业展厅、博物馆、文旅场所、租赁与商演公司；对可靠性与外观要求高、对负载要求低，需求弹性大</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>宇树四足机器人商业消费领域收入增速明显高于科研教育；人形机器人该类占比未单独披露</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>交互服务属规模最大的三个场景之一；娱乐表演的规模份额小于其出货量份额</t>
         </is>
       </c>
     </row>
@@ -2578,17 +2728,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>约4%（轧差）</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>大型制造与物流企业，智能巡检、消防应急等特种作业主体；单价最高、服务占比高，仍处试点</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>宇树2025年前三季度人形机器人收入中工业商用约9%；定制开发产品占比1.71%</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>规模占比最小。参照：宇树2025年前三季度人形机器人收入中工业商用约9%、定制开发1.71%</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2755,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>四足机器人收入占比 76.57%→75.78%→59.53%→42.25%；人形机器人收入占比 0%→1.88%→27.60%→51.53%</t>
+          <t>四足机器人 76.57%→75.78%→59.53%→42.25%；人形机器人 0%→1.88%→27.60%→51.53%</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2622,7 +2772,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>说明：目前尚无机构按统一口径披露全行业各场景的出货量或市场规模占比，占比数据为宇树单家公司口径，不代表全行业结构。</t>
+          <t>数据来源：出货量占比与市场规模排序取自新战略咨询与人形机器人场景应用联盟《2025—2026年度人形机器人产业发展研究报告》（2026-03-30）；三分类框架与宇树单家公司占比取自宇树科技招股文件。两套分类口径不同，不宜混用。</t>
         </is>
       </c>
     </row>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -6818,7 +6818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6832,7 +6832,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>人形机器人产业链企业资本化进度（对应报告第6章、表9—表11）</t>
+          <t>人形机器人产业链企业资本化进度（对应报告第6章、表9—表12）</t>
         </is>
       </c>
     </row>
@@ -7139,27 +7139,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>02692.HK</t>
+          <t>003021.SZ（A股）/ 02692.HK（H股）</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>港交所，2026年3月9日</t>
+          <t>深交所2020年12月4日；港交所2026年3月9日（A+H双重上市）</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A股：招商证券；H股：招商证券国际、德意志银行（联席保荐）</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>微型传动系统与灵巧手模组</t>
+          <t>微型传动与驱动系统解决方案，应用于智能汽车、机器人、消费科技，已布局灵巧手模组</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>发行价71.28港元/股，公开发售认购1,536.76倍，净募资约18.28亿港元，基石含高瓴；上市后一度破发</t>
+          <t>H股发行价71.28港元/股，公开发售认购1,536.76倍，净募资约18.28亿港元，基石含高瓴；上市后一度破发</t>
         </is>
       </c>
     </row>
@@ -7237,812 +7237,738 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>5.2 在审、已受理或已递表（对应表10）</t>
+          <t>5.2 已上市的产业链相关公司一览（按环节，对应报告表10）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>企业</t>
+          <t>产业链环节</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>目标市场</t>
+          <t>已上市公司（代码）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>进度</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>保荐机构</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>核心业务</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>公开信息</t>
-        </is>
-      </c>
+          <t>与无锡巨蟹的关系</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>越疆科技（A股）</t>
+          <t>谐波减速器</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>绿的谐波（688017.SH）、来福谐波（03952.HK）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026/4/27受理，7/22过会</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通（独家保荐）</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>协作机器人、多足与人形机器人</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>大湾区首单H股回A，受理到上会86天；拟募资约12亿元（多足5.5亿、人形2.5亿、营销1亿、补流3亿）；创业板第三套标准</t>
-        </is>
-      </c>
+          <t>直接可比公司与估值参照</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>卧安机器人</t>
+          <t>行星/RV减速器与齿轮</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>港交所</t>
+          <t>中大力德（002896.SZ）、双环传动（002472.SZ）、国茂股份（603915.SH）、丰立智能（301368.SZ）</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>已通过聆讯并完成上市备案</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际＋华泰国际（联席保荐）</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>服务机器人（智能家居执行终端）</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>技术路线相邻；中大力德为智元行星减速器供应商</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>卡诺普机器人</t>
+          <t>无框力矩电机与伺服</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>港交所</t>
+          <t>汇川技术（300124.SZ）、雷赛智能（002979.SZ）、步科股份（688160.SH）、禾川科技（688320.SH）、伟创电气（688698.SH）、昊志机电（300503.SZ）</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2025/11/17首次递表，2026年6月再次递表</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际（独家保荐）</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>工业、协作及具身智能机器人，型号超70款</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>按2025年收入计为中国焊接机器人制造商第一（弗若斯特沙利文）；18C公司；股东含北极光创投、双环传动</t>
-        </is>
-      </c>
+          <t>关节模组的电机与驱动环节</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>智元机器人</t>
+          <t>空心杯电机</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>港交所</t>
+          <t>鸣志电器（603728.SH）、拓邦股份（002139.SZ）、鼎智科技（873593.BJ）</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2026/7/24正式启动赴港上市流程</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>中金公司＋中信证券＋摩根士丹利（承销）</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>远征/灵犀/精灵三大产品线及具身智能基座模型</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>2025年营收10.5亿元；累计量产下线1.5万台；投资人称目标估值400亿—500亿港元</t>
-        </is>
-      </c>
+          <t>灵巧手与末端微型执行器用电机</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>乐聚智能</t>
+          <t>编码器</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>奥普光电（002338.SZ，子公司禹衡光学）</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2026/5/19受理，5/26已问询</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>东方证券</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>轻量化人形机器人</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>2025年全尺寸Kuavo系列销量577台（2024年32台），Omdia与Counterpoint列全球第四；2025年营收2.58亿元，三年营收CAGR 118.68%；最近一轮投后估值43.27亿元；拟募资26亿元，创业板第四套标准首单</t>
-        </is>
-      </c>
+          <t>国内高端编码器主要上市主体，巨蟹自研编码器的对标</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>云深处科技</t>
+          <t>力/力矩与触觉传感器</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>柯力传感（603662.SH）、安培龙（301413.SZ）、东华测试（300354.SZ）</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2025/12/23辅导备案，2026/5/18受理</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>中信建投证券</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>高负载四足机器人及人形机器人</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2025年营收3.37亿元并已盈利；拟募资25.03亿元</t>
-        </is>
-      </c>
+          <t>与巨蟹自研力矩传感器相关</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>一体化关节模组与总成</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>兆威机电（003021.SZ／02692.HK）、富临精工（300432.SZ）、拓普集团（601689.SH）、三花智控（002050.SZ／02050.HK）、震裕科技（300953.SZ）</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>直接竞争环节；富临精工为智元关节模组供应商</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>行星滚柱丝杠与轴承</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>恒立液压（601100.SH）、五洲新春（603667.SH）、贝斯特（300580.SZ）、北特科技（603009.SH）、秦川机床（000837.SZ）、南方精工（002553.SZ）</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>线性执行器路线，与巨蟹旋转关节路线互补</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>5.3 辅导备案或已完成股改（对应表11）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>资本化进度</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>辅导机构</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>核心业务</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>公开财务及估值信息</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>视觉与感知</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>奥比中光（688322.SH）、凌云光（688400.SH）、华依科技（688071.SH）</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>奥比中光为智元3D视觉供应商、华依科技为其IMU供应商</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>芯片与算力</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>地平线机器人（09660.HK）、寒武纪（688256.SH）、瑞芯微（603893.SH）</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>相关度低</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>纽氏达特</t>
+          <t>结构件、代工与制造服务</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2025/12/3辅导备案</t>
+          <t>立讯精密（002475.SZ）、领益智造（002600.SZ）、蓝思科技（300433.SZ／06613.HK）、宁波华翔（002048.SZ）、博众精工（688097.SH）、均普智能（688306.SH）、卧龙电驱（600580.SH）、晋拓股份（603211.SH）</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>东方证券</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>精密传动部件（RV减速器等）</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>与巨蟹同属传动环节</t>
-        </is>
-      </c>
+          <t>多为智元A链核心伙伴</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>天链机器人</t>
+          <t>整机与本体</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>科创板辅导中（第四期）</t>
+          <t>优必选（09880.HK）、宇树科技（688836.SH）、越疆科技（02432.HK，A股在审）、埃斯顿（002747.SZ及H股）、拓斯达（300607.SZ）、埃夫特（688165.SH）、珞石机器人（03752.HK）、乐动机器人（01236.HK）、新睿电子（920211.BJ）、三瑞智能（301696.SZ）</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>华安证券</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人整机</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>下游客户群体</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>傅利叶智能</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>完成E轮融资与股改，已启动科创板辅导准备与申报</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>尚未公开披露</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>GR系列全尺寸人形机器人</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>已实现数百台商业交付</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>由康复机器人切入</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>银河通用</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>已完成股改，计划2026下半年递交港股申请</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>尚未公开披露（拟境外上市）</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>轮式双臂人形机器人及具身智能大模型</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>2026/3完成25亿元D轮（国家大基金参与），累计融资超70亿元，估值约260亿元</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>恒旭资本（海通开元为LP）间接持有</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>资料来源：交易所公开披露及公开资料整理。按与人形机器人产业链的相关度收录，不含仅有概念关联的公司；存在A+H等多地上市的已一并列示。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>星海图</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>已完成股改，最新一轮视为Pre-IPO轮，计划2026年四季度上市</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>尚未公开披露</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>具身智能整机及模型</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>估值超100亿元</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>松延动力</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>已完成股改</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>尚未公开披露</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人本体与仿生人脸</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>2025年总订单超2,500台、合同额超1亿元</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>5.3 在审、已受理或已递表（对应表14）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>目标市场</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>保荐机构</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>核心业务</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>公开信息</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>众擎机器人</t>
+          <t>越疆科技（A股）</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>已完成股改，明确上市计划</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>2026/4/27受理，7/22过会</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>PM01等中小尺寸双足</t>
+          <t>国泰海通（独家保荐）</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>PM01售价8.8万元；与多伦科技2,000台三年框架协议；估值超100亿元</t>
+          <t>协作机器人、多足与人形机器人</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>大湾区首单H股回A，受理到上会86天；拟募资约12亿元（多足5.5亿、人形2.5亿、营销1亿、补流3亿）；创业板第三套标准</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>智平方</t>
+          <t>卧安机器人</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>已完成股改</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>已通过聆讯并完成上市备案</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>AGI原生通用智能机器人</t>
+          <t>国泰君安国际＋华泰国际（联席保荐）</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2026/2 B轮超10亿元后估值超100亿元；2026/6新融资50亿元后估值超200亿元</t>
+          <t>服务机器人（智能家居执行终端）</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>国泰海通B轮联合投资</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>星动纪元</t>
+          <t>卡诺普机器人</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Pre-IPO轮融资25亿元</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>2025/11/17首次递表，2026年6月再次递表</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>具身智能整机，外销灵巧手与半身模组</t>
+          <t>国泰君安国际（独家保荐）</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>估值突破百亿元；总订单超5亿元</t>
+          <t>工业、协作及具身智能机器人，型号超70款</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>按2025年收入计为中国焊接机器人制造商第一（弗若斯特沙利文）；18C公司；股东含北极光创投、双环传动</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>首形科技</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2026/4完成A1轮、7/21完成A2轮，均数亿元</t>
+          <t>港交所</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>2026/7/24正式启动赴港上市流程</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>超仿生类人机器人与仿生情感交互（高仿真"脸"）</t>
+          <t>中金公司＋中信证券＋摩根士丹利（承销）</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>远征/灵犀/精灵三大产品线及具身智能基座模型</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>A2轮由中信金石与吉利资本联合领投，国泰君安创新投等跟投</t>
+          <t>2025年营收10.5亿元；累计量产下线1.5万台；投资人称目标估值400亿—500亿港元</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>魔法原子</t>
+          <t>乐聚智能</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>推进上市进程</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>2026/5/19受理，5/26已问询</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>人形机器人整机</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>轻量化人形机器人</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>最快可能2026年登陆二级市场</t>
+          <t>2025年全尺寸Kuavo系列销量577台（2024年32台），Omdia与Counterpoint列全球第四；2025年营收2.58亿元，三年营收CAGR 118.68%；最近一轮投后估值43.27亿元；拟募资26亿元，创业板第四套标准首单</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；公开融资报道。辅导机构一栏仅纽氏达特与天链机器人已完成辅导备案并公示；其余企业仅完成股改、尚未提交辅导备案，故未公开披露，本报告不作推测。本报告复核后订正首形科技的主营业务及A2轮跟投主体。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>5.4 通过上市公司平台资本化 / IPO终止</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>云深处科技</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2025/12/23辅导备案，2026/5/18受理</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>高负载四足机器人及人形机器人</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2025年营收3.37亿元并已盈利；拟募资25.03亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>5.4 辅导备案或已完成股改（对应表13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>关键时点</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>交易或终止要点</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>资本化进度</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>辅导机构</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>核心业务</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>公开财务及估值信息</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>取得A股上市公司控制权</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>2025/7/8受让29.99%；2025/9/23完成过户</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>"协议转让＋部分要约"合计21亿元取得上纬新材（688585.SH）控股权，智元恒岳及一致行动人合计持股63.62%，邓泰华成为实际控制人；公司称不构成重组上市</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人整机与具身智能</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>叠加2026/7启动的赴港IPO，形成"A股控股平台＋H股IPO"双资本布局</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>节卡股份</t>
+          <t>纽氏达特</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>科创板IPO终止</t>
+          <t>2025/12/3辅导备案</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2023/5受理；2025/12/19撤回，上交所终止审核</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>原计划募资近7亿元；期间多次因财务数据过期中止审核；研发独立性、核心零部件依赖外采、募投产能消化受问询</t>
+          <t>精密传动部件（RV减速器等）</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>协作机器人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>保荐人为国泰海通证券</t>
+          <t>与巨蟹同属传动环节</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：上纬新材公告；上交所审核信息；公开报道。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>天链机器人</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>科创板辅导中（第四期）</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>华安证券</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>傅利叶智能</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>完成E轮融资与股改，已启动科创板辅导准备与申报</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>尚未公开披露</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>GR系列全尺寸人形机器人</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>已实现数百台商业交付</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>由康复机器人切入</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>5.5 资本化整体统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>银河通用</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>已完成股改，2026/3新一轮融资视为Pre-IPO轮，计划2026下半年递交港股申请</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>尚未公开披露（拟境外上市，境内辅导非必经程序）</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>轮式双臂人形机器人及具身智能大模型</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2026/3完成25亿元D轮（国家大基金参与），累计融资超70亿元，估值约260亿元</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本（海通开元为LP）间接持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>星海图</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2026/1完成股改；4月完成20亿元B+轮，计划最快2026年赴港上市</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>尚未公开披露</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>具身智能整机及模型</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>估值超100亿元</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>进入IPO辅导/申报/聆讯/发行阶段的人形机器人核心企业</t>
+          <t>松延动力</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>&gt;20</t>
+          <t>已完成股改</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>截至2026年7月</t>
+          <t>人形机器人本体与仿生人脸</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>2025年总订单超2,500台、合同额超1亿元</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -8054,87 +7980,91 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>中国人形机器人产业股权融资额</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>889</v>
+          <t>众擎机器人</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2026/1/23完成股改；已以保密方式向港交所递表</t>
+        </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>保荐机构：中金公司、中信证券</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>2026年1—4月</t>
+          <t>PM01等中小尺寸双足</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>国泰海通研究</t>
+          <t>B轮2亿美元，河南投资集团汇融基金与立讯精密联合领投，估值破100亿元；PM01售价8.8万元；与多伦科技2,000台三年框架协议</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>已远超2025年全年</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2025年行业融资事件</t>
+          <t>智平方</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>&gt;200</t>
+          <t>已完成股改</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>笔</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>AGI原生通用智能机器人</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>新战略咨询</t>
+          <t>2026/2 B轮超10亿元后估值超100亿元；2026/6新融资50亿元后估值超200亿元</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>总额超500亿元</t>
+          <t>国泰海通B轮联合投资</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>具身智能百亿估值独角兽数量</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>13</v>
+          <t>星动纪元</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Pre-IPO轮融资25亿元</t>
+        </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2026年3月</t>
+          <t>具身智能整机，外销灵巧手与半身模组</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>公开统计</t>
+          <t>估值突破百亿元；总订单超5亿元</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -8146,62 +8076,406 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>科创板第五套标准对具身智能企业的市值要求</t>
+          <t>首形科技</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>≥40</t>
+          <t>2026/4完成A1轮、7/21完成A2轮，均数亿元</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>现行</t>
+          <t>超仿生类人机器人与仿生情感交互（高仿真"脸"）</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>科创板新政</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>创业板第四套标准亦已开放</t>
+          <t>A2轮由中信金石与吉利资本联合领投，国泰君安创新投等跟投</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t>魔法原子</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>推进上市进程</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>尚未公开披露</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>最快可能2026年登陆二级市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；港交所披露文件及公开报道。中介机构按资本化程序分三类：已在证监局完成辅导备案的（纽氏达特—东方证券、天链机器人—华安证券）随备案公示；已聘定保荐机构并递表的（众擎机器人—中金＋中信）可在递表文件或报道中查得；仅完成股改、尚未办理辅导备案且未递表的，法定程序尚未启动、无公开披露渠道，本报告不作推测。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>5.5 通过上市公司平台资本化 / IPO终止</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>关键时点</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>交易或终止要点</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>核心业务</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>智元机器人</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>取得A股上市公司控制权</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>2025/7/8受让29.99%；2025/9/23完成过户</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>"协议转让＋部分要约"合计21亿元取得上纬新材（688585.SH）控股权，智元恒岳及一致行动人合计持股63.62%，邓泰华成为实际控制人；公司称不构成重组上市</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人整机与具身智能</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>叠加2026/7启动的赴港IPO，形成"A股控股平台＋H股IPO"双资本布局</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>节卡股份</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>科创板IPO终止</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2023/5受理；2025/12/19撤回，上交所终止审核</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>原计划募资近7亿元；期间多次因财务数据过期中止审核；研发独立性、核心零部件依赖外采、募投产能消化受问询</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>保荐人为国泰海通证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：上纬新材公告；上交所审核信息；公开报道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>5.6 资本化整体统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>进入IPO辅导/申报/聆讯/发行阶段的人形机器人核心企业</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>&gt;20</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>截至2026年7月</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>公开统计</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>中国人形机器人产业股权融资额</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>889</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>2026年1—4月</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通研究</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>已远超2025年全年</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2025年行业融资事件</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>&gt;200</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>笔</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>新战略咨询</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>总额超500亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>具身智能百亿估值独角兽数量</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>家</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>2026年3月</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>公开统计</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>科创板第五套标准对具身智能企业的市值要求</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>≥40</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>现行</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>科创板新政</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>创业板第四套标准亦已开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>募资规模：宇树（实际）/乐聚（拟）/云深处（拟）/越疆A股（拟）</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>60.99/26/25.03/12</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>2026年</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>发行公告与交易所公告</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8218,7 +8492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8232,14 +8506,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表12—表16）</t>
+          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表13—表17）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>6.1 券商谱系（对应表12）</t>
+          <t>6.1 券商谱系（对应表13）</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8798,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>6.3 已保荐上市（对应表13）</t>
+          <t>6.3 已保荐上市（对应表14）</t>
         </is>
       </c>
     </row>
@@ -8826,7 +9100,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>6.4 正在保荐、在审或辅导（对应表14）</t>
+          <t>6.4 正在保荐、在审或辅导（对应表15）</t>
         </is>
       </c>
     </row>
@@ -8939,7 +9213,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>已通过聆讯并完成上市备案</t>
+          <t>已通过聆讯并完成上市备案，集资约16.4亿港元</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8961,321 +9235,321 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>晋拓股份</t>
+          <t>斯坦德机器人</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2026年度定增</t>
+          <t>港交所上市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
+          <t>2026/6/23递表</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>保荐人（主承销商）</t>
+          <t>联席保荐</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>国泰海通（与中信证券）</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
+          <t>本报告新增。移动机器人（工业物流AMR）及具身智能相关业务</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>智谱</t>
+          <t>晋拓股份</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>A股IPO辅导</t>
+          <t>2026年度定增</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2026年2月重新办理辅导备案</t>
+          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>联合辅导机构</t>
+          <t>保荐人（主承销商）</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>国泰海通（与中金公司）</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>A股IPO辅导</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月重新办理辅导备案</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>联合辅导机构</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>镭神技术</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>A股IPO辅导</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>2026/4/15深圳证监局辅导备案</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>辅导机构</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>国泰海通</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>本报告新增。光通信与半导体精密装备，与机器人产业链非直接相关</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>6.5 曾保荐但已终止（对应报告7.4节）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>原目标板块</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>受理时间</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>终止时间</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>原保荐机构</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>终止原因指向</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>节卡股份</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>上交所科创板</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>2023年5月</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>2025年12月19日撤回，上交所终止审核</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>国泰海通证券</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>6.6 股权投资参股（对应表15）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>6.6 股权投资参股（对应表16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>被投企业</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>投资主体</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>轮次/方式</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>企业定位</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>合并前</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>参与融资</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人整机与具身智能基座模型</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月启动赴港IPO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>智平方</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>国泰君安创新投资</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2026年2月</t>
+          <t>合并前</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>B轮联合投资</t>
+          <t>参与融资</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>AGI原生通用智能机器人</t>
+          <t>人形机器人整机与具身智能基座模型</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
+          <t>2026年7月启动赴港IPO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>首形科技</t>
+          <t>智平方</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>国泰君安创新投</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2026年7月</t>
+          <t>2026年2月</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>A2轮跟投</t>
+          <t>B轮联合投资</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>超仿生类人机器人与仿生情感交互</t>
+          <t>AGI原生通用智能机器人</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
+          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>首形科技</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证裕投资</t>
+          <t>国泰君安创新投</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -9285,218 +9559,218 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>IPO跟投</t>
+          <t>A2轮跟投</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>四足与人形机器人</t>
+          <t>超仿生类人机器人与仿生情感交互</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
+          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>银河通用</t>
+          <t>宇树科技</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本（海通开元为该基金LP）</t>
+          <t>国泰海通证裕投资</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2024—2025年</t>
+          <t>2026年7月</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>间接持有</t>
+          <t>IPO跟投</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>轮式双臂人形机器人</t>
+          <t>四足与人形机器人</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>估值约260亿元</t>
+          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>飒智智能</t>
+          <t>银河通用</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>海通开元（与国元股权联合投资）</t>
+          <t>恒旭资本（海通开元为该基金LP）</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024—2025年</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>A++及A+++轮</t>
+          <t>间接持有</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>智能移动共融机器人</t>
+          <t>轮式双臂人形机器人</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+          <t>估值约260亿元</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>飒智智能</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>海通开元（与国元股权联合投资）</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>A++及A+++轮</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>智能移动共融机器人</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
           <t>某协作机器人研发及生产企业</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>海通创新证券投资</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>0.15亿元</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>协作机器人</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>6.7 产业基金布局（对应表16）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>6.7 产业基金布局（对应表17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>基金名称</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>规模</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>设立/备案时间</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>管理人与主要参与方</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>投资方向</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通中际旭创产业基金</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>首期15亿元</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>2025年9月设立、11月备案</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>光通信、机器人、人工智能</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>国泰海通江城神工基金</t>
+          <t>国泰海通中际旭创产业基金</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>首期2亿元</t>
+          <t>首期15亿元</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025年9月设立、11月备案</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>机器人、智能制造</t>
+          <t>光通信、机器人、人工智能</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -9508,12 +9782,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>科创主题基金矩阵</t>
+          <t>国泰海通江城神工基金</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>累计超700亿元</t>
+          <t>首期2亿元</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9523,29 +9797,29 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>国泰君安创新投资等</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>科技创新（含机器人）</t>
+          <t>机器人、智能制造</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>综合性基金</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本第四期旗舰基金</t>
+          <t>科创主题基金矩阵</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>首轮关账超20亿元</t>
+          <t>累计超700亿元</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9555,179 +9829,191 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
+          <t>国泰君安创新投资等</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>已投银河通用机器人</t>
+          <t>科技创新（含机器人）</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>国泰海通为LP而非GP</t>
+          <t>综合性基金</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>上海三大先导产业母基金（人工智能）</t>
+          <t>恒旭资本第四期旗舰基金</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>225.01亿元</t>
+          <t>首轮关账超20亿元</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>2024年7月</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
+          <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
+          <t>已投银河通用机器人</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>国泰海通仅为出资方之一</t>
+          <t>国泰海通为LP而非GP</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>海通中小企业发展基金</t>
+          <t>上海三大先导产业母基金（人工智能）</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>总规模20亿元</t>
+          <t>225.01亿元</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024年7月</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>海通开元；LP含国家中小企业基金与地方国资</t>
+          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>中早期创业公司（含机器人）</t>
+          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>综合性基金</t>
+          <t>国泰海通仅为出资方之一</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>海通中小企业发展基金</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>总规模20亿元</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>海通开元；LP含国家中小企业基金与地方国资</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>中早期创业公司（含机器人）</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>综合性基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>浦东引领区海通母基金等</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>140亿元</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>海通开元</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>TMT、先进制造等</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>综合性母基金</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>6.8 研究覆盖（非业务关系）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事项</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>行业观点</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr"/>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>公开研报报道</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>行业数据</t>
+          <t>行业观点</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
+          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr"/>
@@ -9735,25 +10021,45 @@
       <c r="E71" s="3" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>国泰海通研究</t>
+          <t>公开研报报道</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>个股观点</t>
+          <t>行业数据</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
+          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr"/>
       <c r="D72" s="3" t="inlineStr"/>
       <c r="E72" s="3" t="inlineStr"/>
       <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>个股观点</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>公开研报报道</t>
         </is>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -7749,7 +7749,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>5.4 辅导备案或已完成股改（对应表13）</t>
+          <t>5.4 辅导备案或已完成股改（对应表12）</t>
         </is>
       </c>
     </row>
@@ -7766,17 +7766,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>辅导机构</t>
+          <t>保荐/辅导机构</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>核心业务</t>
+          <t>券商系股东或投资方（供参考，非保荐关系）</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>公开财务及估值信息</t>
+          <t>核心业务与公开信息</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -7793,27 +7793,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2025/12/3辅导备案</t>
+          <t>已完成辅导备案（2025/12/3）</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>东方证券</t>
+          <t>东方证券（辅导机构）</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
           <t>精密传动部件（RV减速器等）</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>与巨蟹同属传动环节</t>
+          <t>与巨蟹同属精密传动环节</t>
         </is>
       </c>
     </row>
@@ -7830,17 +7830,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>华安证券</t>
+          <t>华安证券（辅导机构）</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
           <t>人形机器人整机</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -7852,108 +7852,108 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>傅利叶智能</t>
+          <t>众擎机器人</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>完成E轮融资与股改，已启动科创板辅导准备与申报</t>
+          <t>2026/1/23完成股改；已以保密方式向港交所递表</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>中金公司、中信证券（保荐机构）</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>GR系列全尺寸人形机器人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>已实现数百台商业交付</t>
+          <t>PM01等中小尺寸双足，售价8.8万元</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>由康复机器人切入</t>
+          <t>B轮2亿美元，河南投资集团汇融基金与立讯精密联合领投，估值破100亿元</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>银河通用</t>
+          <t>傅利叶智能</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>已完成股改，2026/3新一轮融资视为Pre-IPO轮，计划2026下半年递交港股申请</t>
+          <t>2025/7完成股改，已启动科创板辅导准备与申报</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露（拟境外上市，境内辅导非必经程序）</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>轮式双臂人形机器人及具身智能大模型</t>
+          <t>未见券商系股东的公开披露</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2026/3完成25亿元D轮（国家大基金参与），累计融资超70亿元，估值约260亿元</t>
+          <t>GR系列全尺寸人形机器人，由康复机器人切入</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本（海通开元为LP）间接持有</t>
+          <t>已实现数百台商业交付</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>星海图</t>
+          <t>银河通用</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2026/1完成股改；4月完成20亿元B+轮，计划最快2026年赴港上市</t>
+          <t>已完成股改，2026/3新一轮融资视为Pre-IPO轮，计划2026下半年递交港股申请</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>尚未公开披露</t>
+          <t>尚未公开披露（拟境外上市，境内辅导非必经程序）</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>具身智能整机及模型</t>
+          <t>恒旭资本第四期旗舰基金（海通开元为该基金LP）间接持有</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>估值超100亿元</t>
+          <t>轮式双臂人形机器人及具身智能大模型</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026/3融资25亿元（国家大基金参与），累计融资额居国内具身智能领域首位，投后估值超200亿元</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>松延动力</t>
+          <t>星海图</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>已完成股改</t>
+          <t>2026/1完成股改；4月完成20亿元B+轮，计划最快2026年赴港上市</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -7963,56 +7963,56 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>人形机器人本体与仿生人脸</t>
+          <t>B+轮投资方含中金资本旗下基金；另有华登科技、蓝思科技、金融街资本、金浦投资、北京科创等</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>2025年总订单超2,500台、合同额超1亿元</t>
+          <t>具身智能整机及模型，成立于2023年9月</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A轮由蚂蚁集团独家领投，高瓴创投、IDG资本、百度风投等参与；估值突破200亿元</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>众擎机器人</t>
+          <t>星动纪元</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2026/1/23完成股改；已以保密方式向港交所递表</t>
+          <t>Pre-IPO轮融资25亿元</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>保荐机构：中金公司、中信证券</t>
+          <t>尚未公开披露</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>PM01等中小尺寸双足</t>
+          <t>未见券商系股东的公开披露；主要投资方为联想创投、清流资本、源码资本、阿里巴巴、金鼎资本等</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>B轮2亿美元，河南投资集团汇融基金与立讯精密联合领投，估值破100亿元；PM01售价8.8万元；与多伦科技2,000台三年框架协议</t>
+          <t>具身智能整机，外销灵巧手与半身模组</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>估值突破百亿元；总订单超5亿元</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>智平方</t>
+          <t>松延动力</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8027,29 +8027,29 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>AGI原生通用智能机器人</t>
+          <t>投资方含中金战新创业投资（鹤山）合伙企业、北京机器人产业发展投资基金</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2026/2 B轮超10亿元后估值超100亿元；2026/6新融资50亿元后估值超200亿元</t>
+          <t>人形机器人本体与仿生人脸</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>国泰海通B轮联合投资</t>
+          <t>2025年总订单超2,500台、合同额超1亿元</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>星动纪元</t>
+          <t>智平方</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Pre-IPO轮融资25亿元</t>
+          <t>已完成股改</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>具身智能整机，外销灵巧手与半身模组</t>
+          <t>投资方含中金资本、中信建投、国泰海通，以及招商局资本、洪泰资本、金沙江联合资本、博华资本、航信资本等</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>估值突破百亿元；总订单超5亿元</t>
+          <t>AGI原生通用智能机器人</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026/2 B轮超10亿元、估值超100亿元；6月新一轮后超200亿元，为大湾区最大具身智能独角兽</t>
         </is>
       </c>
     </row>
@@ -8091,17 +8091,17 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
+          <t>A2轮跟投方含中信证券国际资本、国泰君安创新投；中信金石与吉利资本联合领投</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
           <t>超仿生类人机器人与仿生情感交互（高仿真"脸"）</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>A2轮由中信金石与吉利资本联合领投，国泰君安创新投等跟投</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
+          <t>未见券商系股东的公开披露；由魔法工场（无锡）科技有限公司全资持股</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
           <t>人形机器人整机</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -8140,7 +8140,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；证监会及各地证监局辅导备案公示；港交所披露文件及公开报道。中介机构按资本化程序分三类：已在证监局完成辅导备案的（纽氏达特—东方证券、天链机器人—华安证券）随备案公示；已聘定保荐机构并递表的（众擎机器人—中金＋中信）可在递表文件或报道中查得；仅完成股改、尚未办理辅导备案且未递表的，法定程序尚未启动、无公开披露渠道，本报告不作推测。</t>
+          <t>数据来源：Wind整理成果；证监会及各地证监局辅导备案公示；港交所披露文件；公开融资报道及企业工商信息。"券商系股东或投资方"系通过股东穿透与融资报道整理，仅反映券商与企业已有股权层面接触，不代表已建立保荐或辅导关系，两者不可相互推定。</t>
         </is>
       </c>
     </row>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -6888,12 +6888,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>港交所，2023年12月</t>
+          <t>港交所，2023年12月29日</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际（联席保荐）</t>
+          <t>国泰君安国际（独家保荐）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>港交所，2024年12月</t>
+          <t>港交所，2024年12月23日</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际（联席保荐）</t>
+          <t>国泰君安国际、农银国际（联席保荐）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>招银国际融资（独家保荐）</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2025年营收2.61亿元、销量29.15万台、均价571元/台、亏损1.71亿元；发行前估值约15亿元</t>
+          <t>2025年营收2.61亿元、销量29.15万台、均价571元/台、亏损1.71亿元；发行前估值约15亿元；上市首日涨3.16%、市值超91亿港元；10家基石含橡树资本、嘉实、鼎晖、易方达</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>港交所，2023年12月</t>
+          <t>港交所，2023年12月29日</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>联席保荐</t>
+          <t>独家保荐</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>港交所，2024年12月</t>
+          <t>港交所，2024年12月23日</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际</t>
+          <t>国泰君安国际（与农银国际）</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -769,7 +769,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>报告图1—图9制图数据</t>
+          <t>报告图1—图8制图数据</t>
         </is>
       </c>
     </row>
@@ -1957,144 +1957,6 @@
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>数据来源：智元机器人公开披露及媒体报道。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>图9  国泰海通系与人形机器人产业链公司的关联分布（条形图）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>关联类型</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>公司/基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>已保荐上市</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>绿的谐波、步科股份、优必选、越疆科技(港)、三瑞智能、乐动机器人、新睿电子、珞石机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>正在保荐/在审/辅导</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>越疆科技(A股)、卡诺普机器人、卧安机器人、晋拓股份(定增)、智谱(辅导)、镭神技术(辅导)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>曾保荐但终止</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>节卡股份</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>股权投资参股</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>家</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人、智平方、首形科技、宇树科技、银河通用(间接)、飒智智能、某协作机器人企业</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>产业基金覆盖</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>中际旭创产业基金、江城神工基金、科创主题基金矩阵、恒旭资本第四期、上海AI母基金、海通中小企业发展基金、浦东引领区海通母基金等</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：本报告基于表13至表16统计。前四项单位为家、末项为只；产业基金多为综合性股权投资基金，机器人仅为其投资方向之一。</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7373,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>5.3 在审、已受理或已递表（对应表14）</t>
+          <t>5.3 在审、已受理或已递表（对应表13）</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8506,508 +8368,580 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表13—表17）</t>
+          <t>与国泰海通系相关的机器人产业链公司（对应报告第7章、表13—表16）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>6.1 券商谱系（对应表13）</t>
+          <t>6.1 整体投行位置（供内部参考；报告正文已按批注删除该节）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>券商主体</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>存续时间</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>与人形机器人产业链的关系</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>国泰证券</t>
+          <t>A股IPO保荐上市数量</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1992/9—1999/8</t>
+          <t>13单，行业第一，市占率约18.3%</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>在上海成立，国泰君安前身之一。存续期间人形机器人产业尚未兴起，无直接保荐或投资关联</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>2026年上半年</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>券商IPO保荐半年度统计</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>君安证券</t>
+          <t>A股IPO承销金额</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1992/10—1999/8</t>
+          <t>646亿元，行业第三</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>在深圳成立，国泰君安前身之一。存续期间人形机器人产业尚未兴起，无直接保荐或投资关联</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>2026年上半年</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>国泰君安证券</t>
+          <t>IPO受理与在审家数</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1999/8—2025/3</t>
+          <t>与华泰联合并列前二</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2015年A股上市（601211.SH），2017年H股上市（2611.HK）。保荐绿的谐波、优必选、越疆科技（港股经国泰君安国际）等</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
+          <t>2026年上半年</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>海通证券</t>
+          <t>前沿产业（AI、集成电路等）累计投资</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1988—2025/3</t>
+          <t>305个项目、约200亿元</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2007年A股上市（600837.SH），2012年H股上市（6837.HK）。保荐步科股份、新睿电子等</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
+          <t>截至2026年</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通公开披露</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券</t>
+          <t>累计服务科创板上市企业</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2025/3合并、4月更名至今</t>
+          <t>107家、承销规模超2,100亿元，行业第一</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>国泰君安换股吸收合并海通证券，注册资本176.3亿元，净资产行业第一</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>截至2026年</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通公开披露</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>资料来源：各券商公开披露。国泰证券与君安证券的存续期远早于人形机器人产业兴起，本表所列关联均发生于国泰君安、海通证券及国泰海通期间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>6.2 整体投行位置</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>口径</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>6.2 已保荐上市（对应表13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>上市地与时间</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>保荐角色</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>归属主体</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>绿的谐波</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>688017.SH</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>科创板，2020年8月</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>谐波减速器国内龙头</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>A股IPO保荐上市数量</t>
+          <t>步科股份</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>13单，行业第一，市占率约18.3%</t>
+          <t>688160.SH</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
+          <t>科创板，2020年11月</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>券商IPO保荐半年度统计</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>海通证券</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>伺服与无框力矩电机</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>A股IPO承销金额</t>
+          <t>优必选</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>646亿元，行业第三</t>
+          <t>09880.HK</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
+          <t>港交所，2023年12月29日</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>人形机器人第一股</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>IPO受理与在审家数</t>
+          <t>越疆科技</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>与华泰联合并列前二</t>
+          <t>02432.HK</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年</t>
+          <t>港交所，2024年12月23日</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际（与农银国际）</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人第一股，18C首家H股</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>前沿产业（AI、集成电路等）累计投资</t>
+          <t>三瑞智能</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>305个项目、约200亿元</t>
+          <t>301696.SZ</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>截至2026年</t>
+          <t>创业板，2026年4月10日</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通公开披露</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。无人机与机器人动力系统（电机、模组）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>累计服务科创板上市企业</t>
+          <t>乐动机器人</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>107家、承销规模超2,100亿元，行业第一</t>
+          <t>01236.HK</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>截至2026年</t>
+          <t>港交所，2026年5月11日</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通公开披露</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>海通国际＋国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>集资约8.8亿港元，首日涨约102%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>北交所，2026年6月5日</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（原海通承做）</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>工业机器人控制系统</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>6.3 已保荐上市（对应表14）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>珞石机器人</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>03752.HK</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>港交所，2026年7月9日</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>18C特专科技公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>6.3 正在保荐、在审或辅导（对应表14）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>上市地与时间</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>保荐角色</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>归属主体</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>绿的谐波</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>688017.SH</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>科创板，2020年8月</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>保荐承销</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>谐波减速器国内龙头</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>步科股份</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>688160.SH</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>科创板，2020年11月</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>保荐承销</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>海通证券</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>伺服与无框力矩电机</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>优必选</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>09880.HK</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>港交所，2023年12月29日</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>独家保荐</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人第一股</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>业务定位与相关性</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>越疆科技</t>
+          <t>越疆科技（A股）</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>02432.HK</t>
+          <t>创业板IPO（H股回A）</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>港交所，2024年12月23日</t>
+          <t>2026/4/27受理，7/22过会</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>联席保荐</t>
+          <t>独家保荐</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际（与农银国际）</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>协作机器人第一股，18C首家H股</t>
+          <t>协作机器人，拟募资12亿元含人形机器人技术提升2.5亿元</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>三瑞智能</t>
+          <t>卡诺普机器人</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>301696.SZ</t>
+          <t>港交所18C上市</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>创业板，2026年4月10日</t>
+          <t>2025/11/17首次递表，2026年6月再次递表</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>保荐承销</t>
+          <t>独家保荐</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>国泰君安国际</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。无人机与机器人动力系统（电机、模组）</t>
+          <t>中国焊接机器人制造商第一，已布局具身智能机器人</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>乐动机器人</t>
+          <t>卧安机器人</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>01236.HK</t>
+          <t>港交所上市</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>港交所，2026年5月11日</t>
+          <t>已通过聆讯并完成上市备案，集资约16.4亿港元</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -9017,635 +8951,635 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>海通国际＋国泰君安国际</t>
+          <t>国泰君安国际（与华泰国际）</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>集资约8.8亿港元，首日涨约102%</t>
+          <t>服务机器人</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>新睿电子</t>
+          <t>斯坦德机器人</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>920211.BJ</t>
+          <t>港交所上市</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>北交所，2026年6月5日</t>
+          <t>2026/6/23递表</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>独家保荐</t>
+          <t>联席保荐</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通（原海通承做）</t>
+          <t>国泰海通（与中信证券）</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>工业机器人控制系统</t>
+          <t>本报告新增。移动机器人（工业物流AMR）及具身智能相关业务</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>珞石机器人</t>
+          <t>晋拓股份</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>03752.HK</t>
+          <t>2026年度定增</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>港交所，2026年7月9日</t>
+          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>联席保荐</t>
+          <t>保荐人（主承销商）</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际（与中金公司）</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>18C特专科技公司</t>
+          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>A股IPO辅导</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月重新办理辅导备案</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>联合辅导机构</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>镭神技术</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>A股IPO辅导</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2026/4/15深圳证监局辅导备案</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>辅导机构</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。光通信与半导体精密装备，与机器人产业链非直接相关</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>6.4 正在保荐、在审或辅导（对应表15）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>6.4 曾保荐但已终止（对应报告7.4节）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>企业</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>进度</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>归属主体</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>业务定位与相关性</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>越疆科技（A股）</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>创业板IPO（H股回A）</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>2026/4/27受理，7/22过会</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>独家保荐</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>协作机器人，拟募资12亿元含人形机器人技术提升2.5亿元</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>卡诺普机器人</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>港交所18C上市</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>2025/11/17首次递表，2026年6月再次递表</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>独家保荐</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>中国焊接机器人制造商第一，已布局具身智能机器人</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>原目标板块</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>受理时间</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>终止时间</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>原保荐机构</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>终止原因指向</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>卧安机器人</t>
+          <t>节卡股份</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>港交所上市</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>已通过聆讯并完成上市备案，集资约16.4亿港元</t>
+          <t>2023年5月</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>联席保荐</t>
+          <t>2025年12月19日撤回，上交所终止审核</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>国泰君安国际（与华泰国际）</t>
+          <t>国泰海通证券</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>服务机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>斯坦德机器人</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>港交所上市</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>2026/6/23递表</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>联席保荐</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通（与中信证券）</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。移动机器人（工业物流AMR）及具身智能相关业务</t>
+          <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>晋拓股份</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>2026年度定增</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>保荐人（主承销商）</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>智谱</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>A股IPO辅导</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>2026年2月重新办理辅导备案</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>联合辅导机构</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通（与中金公司）</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>6.5 股权投资参股（对应表15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>被投企业</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>投资主体</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>轮次/方式</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>企业定位</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>镭神技术</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>A股IPO辅导</t>
+          <t>国泰君安创新投资</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2026/4/15深圳证监局辅导备案</t>
+          <t>合并前</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>辅导机构</t>
+          <t>参与融资</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
+          <t>人形机器人整机与具身智能基座模型</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月启动赴港IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>智平方</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>国泰海通</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。光通信与半导体精密装备，与机器人产业链非直接相关</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>B轮联合投资</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>AGI原生通用智能机器人</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>首形科技</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>A2轮跟投</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>超仿生类人机器人与仿生情感交互</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>6.5 曾保荐但已终止（对应报告7.4节）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>原目标板块</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>受理时间</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>终止时间</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>原保荐机构</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>终止原因指向</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>宇树科技</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证裕投资</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>IPO跟投</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>四足与人形机器人</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>银河通用</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本（海通开元为该基金LP）</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>2024—2025年</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>间接持有</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>轮式双臂人形机器人</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>估值约260亿元</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>节卡股份</t>
+          <t>飒智智能</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>海通开元（与国元股权联合投资）</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2023年5月</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>2025年12月19日撤回，上交所终止审核</t>
+          <t>A++及A+++轮</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券</t>
+          <t>智能移动共融机器人</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
+          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>某协作机器人研发及生产企业</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>海通创新证券投资</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>0.15亿元</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>6.6 股权投资参股（对应表16）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>被投企业</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>投资主体</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>轮次/方式</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>企业定位</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>合并前</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>参与融资</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人整机与具身智能基座模型</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月启动赴港IPO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>智平方</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>2026年2月</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>B轮联合投资</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>AGI原生通用智能机器人</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>6.6 产业基金布局（对应表16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>基金名称</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>设立/备案时间</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>管理人与主要参与方</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>投资方向</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>首形科技</t>
+          <t>国泰海通中际旭创产业基金</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>国泰君安创新投</t>
+          <t>首期15亿元</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>2026年7月</t>
+          <t>2025年9月设立、11月备案</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>A2轮跟投</t>
+          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>超仿生类人机器人与仿生情感交互</t>
+          <t>光通信、机器人、人工智能</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>宇树科技</t>
+          <t>国泰海通江城神工基金</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证裕投资</t>
+          <t>首期2亿元</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2026年7月</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>IPO跟投</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>四足与人形机器人</t>
+          <t>机器人、智能制造</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>银河通用</t>
+          <t>科创主题基金矩阵</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本（海通开元为该基金LP）</t>
+          <t>累计超700亿元</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2024—2025年</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>间接持有</t>
+          <t>国泰君安创新投资等</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>轮式双臂人形机器人</t>
+          <t>科技创新（含机器人）</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>估值约260亿元</t>
+          <t>综合性基金</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>飒智智能</t>
+          <t>恒旭资本第四期旗舰基金</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>海通开元（与国元股权联合投资）</t>
+          <t>首轮关账超20亿元</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -9655,411 +9589,205 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>A++及A+++轮</t>
+          <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>智能移动共融机器人</t>
+          <t>已投银河通用机器人</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+          <t>国泰海通为LP而非GP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>某协作机器人研发及生产企业</t>
+          <t>上海三大先导产业母基金（人工智能）</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>海通创新证券投资</t>
+          <t>225.01亿元</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通仅为出资方之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>海通中小企业发展基金</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>总规模20亿元</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>海通开元；LP含国家中小企业基金与地方国资</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>中早期创业公司（含机器人）</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>综合性基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>浦东引领区海通母基金等</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>140亿元</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
           <t>2023年</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>0.15亿元</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>协作机器人</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>海通开元</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>TMT、先进制造等</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>综合性母基金</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>6.7 产业基金布局（对应表17）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>基金名称</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>规模</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>设立/备案时间</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>管理人与主要参与方</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>投资方向</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通中际旭创产业基金</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>首期15亿元</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>2025年9月设立、11月备案</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>光通信、机器人、人工智能</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通江城神工基金</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>首期2亿元</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>机器人、智能制造</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>6.7 研究覆盖（非业务关系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>科创主题基金矩阵</t>
+          <t>行业观点</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>累计超700亿元</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资等</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>科技创新（含机器人）</t>
-        </is>
-      </c>
+          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>综合性基金</t>
+          <t>公开研报报道</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>恒旭资本第四期旗舰基金</t>
+          <t>行业数据</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>首轮关账超20亿元</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>已投银河通用机器人</t>
-        </is>
-      </c>
+          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>国泰海通为LP而非GP</t>
+          <t>国泰海通研究</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>上海三大先导产业母基金（人工智能）</t>
+          <t>个股观点</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>225.01亿元</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>2024年7月</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
-        </is>
-      </c>
+          <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通仅为出资方之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>海通中小企业发展基金</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>总规模20亿元</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>海通开元；LP含国家中小企业基金与地方国资</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>中早期创业公司（含机器人）</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>综合性基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>浦东引领区海通母基金等</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>140亿元</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>2023年</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>海通开元</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>TMT、先进制造等</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>综合性母基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>6.8 研究覆盖（非业务关系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>行业观点</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>公开研报报道</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>行业数据</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr"/>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通研究</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>个股观点</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>公开研报报道</t>
         </is>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -8354,7 +8354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8819,975 +8819,1199 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>卧安机器人</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>港交所主板，2026年上市</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际（与华泰国际）</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>服务机器人（智能家居执行终端），集资规模约16.4亿港元。本轮由表14移入</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>国茂股份</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>603915.SH</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>上交所主板，2019年6月14日</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。通用减速机</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>6.3 正在保荐、在审或辅导（对应表14）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>进度</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>归属主体</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>业务定位与相关性</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>伟创电气</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>688698.SH</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>科创板，2020年12月29日</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。变频器与伺服系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>丰立智能</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>301368.SZ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>创业板，2022年12月15日</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>保荐承销</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安（现国泰海通）</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。精密齿轮与传动部件；2025年度定增亦由国泰海通保荐</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>越疆科技（A股）</t>
+          <t>永贵电器</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>创业板IPO（H股回A）</t>
+          <t>300351.SZ</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2026/4/27受理，7/22过会</t>
+          <t>创业板，2012年9月20日</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>独家保荐</t>
+          <t>保荐承销</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>国泰君安</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>协作机器人，拟募资12亿元含人形机器人技术提升2.5亿元</t>
+          <t>本报告新增。连接器；保荐机构以委托方口径列示，未从公开渠道核到发行时保荐主体名称</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>卡诺普机器人</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>港交所18C上市</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>2025/11/17首次递表，2026年6月再次递表</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>独家保荐</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>中国焊接机器人制造商第一，已布局具身智能机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>卧安机器人</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>港交所上市</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>已通过聆讯并完成上市备案，集资约16.4亿港元</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>联席保荐</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安国际（与华泰国际）</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>服务机器人</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>斯坦德机器人</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>港交所上市</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>2026/6/23递表</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>联席保荐</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通（与中信证券）</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。移动机器人（工业物流AMR）及具身智能相关业务</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>晋拓股份</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>2026年度定增</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>保荐人（主承销商）</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>6.3 正在保荐、在审或辅导（对应表14）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>进度</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>归属主体</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>业务定位与相关性</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>智谱</t>
+          <t>越疆科技（A股）</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A股IPO辅导</t>
+          <t>创业板IPO（H股回A）</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2026年2月重新办理辅导备案</t>
+          <t>2026/4/27受理，7/22过会</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>联合辅导机构</t>
+          <t>独家保荐</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>国泰海通（与中金公司）</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
+          <t>协作机器人，拟募资12亿元含人形机器人技术提升2.5亿元</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>镭神技术</t>
+          <t>卡诺普机器人</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>港交所18C上市</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>2025/11/17首次递表，2026年6月再次递表</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>独家保荐</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安国际</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>中国焊接机器人制造商第一，已布局具身智能机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>斯坦德机器人</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>港交所上市</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>2026/6/23首次递表，2026/7/27重新递表</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>联席保荐</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（与中信证券）</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>移动机器人（工业物流AMR）及具身智能相关业务</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>金道科技</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>可转换公司债券发行</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>在审</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>保荐人（主承销商）</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。齿轮传动部件，与关节模组传动环节相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>晋拓股份</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026年度定增</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月获上交所受理，拟发行不超8,154.24万股、募资不超5亿元</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>保荐人（主承销商）</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。铝合金精密压铸件，已服务UR、云迹、节卡，布局人形机器人零部件</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>智谱</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>A股IPO辅导</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>2026/4/15深圳证监局辅导备案</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>辅导机构</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>本报告新增。光通信与半导体精密装备，与机器人产业链非直接相关</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>6.4 曾保荐但已终止（对应报告7.4节）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>企业</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>原目标板块</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>受理时间</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>终止时间</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>原保荐机构</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>终止原因指向</t>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2026年2月重新办理辅导备案</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>联合辅导机构</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通（与中金公司）</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>本报告新增。人工智能大模型，与具身智能"大脑"层相关</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>节卡股份</t>
+          <t>镭神技术（弱相关，上游设备）</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>A股IPO辅导</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2023年5月</t>
+          <t>2026/4/15深圳证监局辅导备案</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>2025年12月19日撤回，上交所终止审核</t>
+          <t>辅导机构</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>6.5 股权投资参股（对应表15）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>被投企业</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>投资主体</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>轮次/方式</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>企业定位</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>智元机器人</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投资</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>合并前</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>参与融资</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>人形机器人整机与具身智能基座模型</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月启动赴港IPO</t>
+          <t>光通信与半导体精密装备，属上游设备、与机器人产业链弱相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>6.4 曾保荐但已终止（对应报告7.4节）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>原目标板块</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>受理时间</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>终止时间</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>原保荐机构</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>终止原因指向</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>智平方</t>
+          <t>节卡股份</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>2026年2月</t>
+          <t>2023年5月</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>B轮联合投资</t>
+          <t>2025年12月19日撤回，上交所终止审核</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>AGI原生通用智能机器人</t>
+          <t>国泰海通证券</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>首形科技</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>国泰君安创新投</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>A2轮跟投</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>超仿生类人机器人与仿生情感交互</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
+          <t>研发独立性、核心零部件依赖外采、募投项目产能消化；原计划募资近7亿元</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>宇树科技</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通证裕投资</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>2026年7月</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>IPO跟投</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>四足与人形机器人</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>证裕投资为另类投资子公司；国泰君安创新投资此前亦通过旗下基金参与</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>银河通用</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>恒旭资本（海通开元为该基金LP）</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>2024—2025年</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>间接持有</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>轮式双臂人形机器人</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>估值约260亿元</t>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>6.5 股权投资参股（对应表15）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>被投企业</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>投资主体</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>轮次/方式</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>企业定位</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>飒智智能</t>
+          <t>智元机器人</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>海通开元（与国元股权联合投资）</t>
+          <t>国泰君安创新投资</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>合并前</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>A++及A+++轮</t>
+          <t>参与融资</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>智能移动共融机器人</t>
+          <t>人形机器人整机与具身智能基座模型</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
+          <t>2026年7月启动赴港IPO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>某协作机器人研发及生产企业</t>
+          <t>智平方</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>海通创新证券投资</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2023年</t>
+          <t>2026年2月</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.15亿元</t>
+          <t>B轮联合投资</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>协作机器人</t>
+          <t>AGI原生通用智能机器人</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
+          <t>B轮后估值超100亿元，2026年6月新一轮后超200亿元</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>首形科技</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>A2轮跟投</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>超仿生类人机器人与仿生情感交互</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>本报告订正：原表述为"国泰海通"跟投、业务为"人形机器人核心部件"</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>宇树科技</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证裕投资</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>IPO跟投（待核实）</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>四足与人形机器人</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>该项跟投未从交易所发行公告或公司公告中核到，暂列为待核实事项；正式使用前须以发行结果公告的战略配售名单复核</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>6.6 产业基金布局（对应表16）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>基金名称</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>规模</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>设立/备案时间</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>管理人与主要参与方</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>投资方向</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>银河通用</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>恒旭资本（直接投资）；海通开元、国泰君安证裕通过恒旭基金LP份额形成间接敞口</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>2024—2025年</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>间接敞口</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>轮式双臂人形机器人及具身智能大模型</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>穿透比例未披露；投后估值超200亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>飒智智能</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>海通开元（与国元股权联合投资）</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>A++及A+++轮</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>智能移动共融机器人</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>产品含多模态协同作业机器人、复合机器人、类人作业移动双臂机器人</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>国泰海通中际旭创产业基金</t>
+          <t>灵猴机器人</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>首期15亿元</t>
+          <t>国泰君安创新投资</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>2025年9月设立、11月备案</t>
+          <t>2026年</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
+          <t>B轮及B+轮</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>光通信、机器人、人工智能</t>
+          <t>具身智能核心零部件</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>本报告新增</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>国泰海通江城神工基金</t>
+          <t>赛那德</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>首期2亿元</t>
+          <t>海通开元</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026年6月</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>C轮</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>机器人、智能制造</t>
+          <t>物流具身智能机器人</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>本报告新增</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
+          <t>某协作机器人研发及生产企业</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>海通创新证券投资</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>0.15亿元</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>协作机器人</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>产品通过CE和SEMI认证，应用于汽车、能源、半导体、3C等；公开资料未披露企业名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>6.6 产业基金布局（对应表16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>基金名称</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>设立/备案时间</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>管理人与主要参与方</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>投资方向</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通中际旭创产业基金</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>首期15亿元</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>2025年9月设立、11月备案</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>国泰君安创新投资与江苏乾融；中际旭创出资3.54亿元（23.6%）</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>光通信、机器人、人工智能</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通江城神工基金</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>首期2亿元</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>机器人、智能制造</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>科创主题基金矩阵</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>累计超700亿元</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>国泰君安创新投资等</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>科技创新（含机器人）</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>综合性基金</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>恒旭资本第四期旗舰基金</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>首轮关账超20亿元</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>恒旭资本；LP含国泰君安证裕、海通开元</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>已投银河通用机器人</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>国泰海通为LP而非GP</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>上海三大先导产业母基金（人工智能）</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>225.01亿元</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>2024年7月</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>上海国投先导；海通创新证券投资出资2.5亿元</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通仅为出资方之一</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>海通中小企业发展基金</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>总规模20亿元</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>海通开元；LP含国家中小企业基金与地方国资</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>中早期创业公司（含机器人）</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>综合性基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>浦东引领区海通母基金等</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>140亿元</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>2023年</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>海通开元</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>TMT、先进制造等</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>综合性母基金</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>6.7 研究覆盖（非业务关系）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>事项</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>行业观点</t>
+          <t>上海三大先导产业母基金（人工智能）</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr"/>
+          <t>225.01亿元</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>2024年7月</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>上海国投先导；国泰君安证裕出资2.5亿元、海通创新证券投资出资2.5亿元</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>智能芯片、智能软件、自动驾驶、智能机器人</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>公开研报报道</t>
+          <t>国泰海通体系合计出资5亿元</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>行业数据</t>
+          <t>海通中小企业发展基金</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
+          <t>总规模20亿元</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>海通开元；LP含国家中小企业基金与地方国资</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>中早期创业公司（含机器人）</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>国泰海通研究</t>
+          <t>综合性基金</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>浦东引领区海通母基金等</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>140亿元</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>海通开元</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>TMT、先进制造等</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>综合性母基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：一、上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额；二、投资主体沿革——2026年6月30日海通创新证券投资有限公司吸收合并国泰君安证裕投资有限公司并更名为国泰海通证裕投资有限公司，海通开元投资与国泰君安创新投资的整合亦已启动，本表按交易发生时的名称列示，不作追溯调整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>6.7 研究覆盖（非业务关系）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>事项</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>行业观点</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>看好机器人感知系统、核心零部件与本体厂商，建议关注丝杠、轻量化材料等核心零部件方向</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>公开研报报道</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>行业数据</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2026年前4个月中国人形机器人产业股权融资累计889亿元，远超2025年全年</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
           <t>个股观点</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>2026年4月将优必选目标价上调至184.77港元；首予地平线机器人-W（09660）"增持"评级</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>公开研报报道</t>
         </is>

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -2322,7 +2322,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>工业和信息化主管部门/新华网</t>
+          <t>第三方行业统计与公开报道</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2025年，约占全国1/6</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>公开报道</t>
+          <t>公开报道；江苏为国内重要产业集聚区</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4252,17 +4252,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>编码器占单个关节模组成本</t>
+          <t>编码器单机用量</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>10~20</t>
+          <t>关节普遍采用双编码器，单机用量较大，是关节感知与闭环控制的重要成本组成部分</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4272,68 +4272,68 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>编码器占整机硬件成本</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>7~8</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>行业测算</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+          <t>本报告整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>3.4 力/力矩传感器环节（对应报告表3；依批注由其他环节移入核心环节）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>数值/内容</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>年度/口径</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>中国六维力传感器市场规模</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>&gt;3</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
@@ -4343,10 +4343,8 @@
           <t>中国六维力传感器市场规模</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>&gt;3</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>3.88</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -4355,7 +4353,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>2026年预测</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4367,20 +4365,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>中国六维力传感器市场规模</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>3.88</v>
+          <t>应变片技术市场份额</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>&gt;80</t>
+        </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2026年预测</t>
+          <t>当前</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -4392,69 +4392,69 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>应变片技术市场份额</t>
+          <t>MEMS方案体积</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>&gt;80</t>
+          <t>可降至传统产品的1/10</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>当前</t>
+          <t>在研</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>宇立仪器、坤维科技</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MEMS方案体积</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>可降至传统产品的1/10</t>
-        </is>
+          <t>蓝点触控高维解耦模型训练样本</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>53</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
+          <t>万个样本点</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>宇立仪器、坤维科技</t>
+          <t>公开报道</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>蓝点触控高维解耦模型训练样本</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>53</v>
+          <t>坤维科技标定技术</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>六轴联合加载标定</t>
+        </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>万个样本点</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -4471,12 +4471,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>坤维科技标定技术</t>
+          <t>关节内置力矩传感器供给方式</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>六轴联合加载标定</t>
+          <t>多由关节模组厂商自研并随模组交付，独立外售规模有限</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -4491,19 +4491,19 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>公开报道</t>
+          <t>本报告整理</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>关节内置力矩传感器供给方式</t>
+          <t>代表企业—六维力传感器</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>多由关节模组厂商自研并随模组交付，独立外售规模有限</t>
+          <t>坤维科技、宇立仪器、蓝点触控、柯力传感、安培龙</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -4518,19 +4518,19 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>本报告整理</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>代表企业—六维力传感器</t>
+          <t>代表企业—关节内置力矩传感器</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>坤维科技、宇立仪器、蓝点触控、柯力传感、安培龙</t>
+          <t>无锡巨蟹、绿的谐波等关节模组厂商自研</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4545,83 +4545,81 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>行业研究</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>代表企业—关节内置力矩传感器</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>无锡巨蟹、绿的谐波等关节模组厂商自研</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
           <t>公开资料</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>3.5 一体化关节模组环节</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>年度/口径</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>全球关节模组需求量</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>万个</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>行业白皮书</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>全球关节模组需求量</t>
+          <t>其中国产人形整机需求占比</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>万个</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4638,20 +4636,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>其中国产人形整机需求占比</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>70</v>
+          <t>全球头部整机企业合计规划产能</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>&gt;10</t>
+        </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>万台</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>2026年</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>全球头部整机企业合计规划产能</t>
+          <t>预计实际交付规模</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>&gt;10</t>
+          <t>4~6</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>2026年（行业机构预测）</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -4690,22 +4690,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>预计实际交付规模</t>
+          <t>关节模组占整机BOM成本</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>4~6</t>
+          <t>35~60</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>万台</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -4717,17 +4717,15 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>关节模组占整机BOM成本</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>35~60</t>
-        </is>
+          <t>Optimus Gen2整机硬件成本</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -4737,22 +4735,22 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>行业白皮书</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Optimus Gen2整机硬件成本</t>
+          <t>—其中28个一体化关节模组占比</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4769,15 +4767,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>—其中28个一体化关节模组占比</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>54</v>
+          <t>—单套关节模组价格区间</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>4000~6500</t>
+        </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -4794,105 +4794,103 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>—单套关节模组价格区间</t>
+          <t>2030年头部企业数量与合计份额</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>4000~6500</t>
+          <t>5~8家占80%以上（行业机构预测，非确定结果）</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>元</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
+          <t>2030年预测</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>行业白皮书</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.6 其他上游环节（对应报告表5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>关键数据</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>年度/口径</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>行星滚柱丝杠占整机BOM成本</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>近20</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>行业测算</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>2030年头部企业数量与合计份额</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>5~8家占80%以上</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>2030年预测</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>行业白皮书</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>3.6 其他上游环节（对应报告表5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>环节</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>关键数据</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>年度/口径</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>来源</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>行星滚柱丝杠占整机BOM成本</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>近20</t>
-        </is>
+          <t>Optimus单台行星滚柱丝杠用量</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>个</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -4909,75 +4907,75 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Optimus单台行星滚柱丝杠用量</t>
+          <t>全球人形机器人用行星滚柱丝杠收入规模</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>14</v>
+        <v>30.1</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2024年</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>第三方研究</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>全球人形机器人用行星滚柱丝杠收入规模</t>
+          <t>灵巧手占整机成本</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>30.1</v>
+        <v>15</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>第三方研究</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>灵巧手占整机成本</t>
+          <t>全球人形机器人灵巧手市场规模</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2025年（机构测算，较高出货增长假设）</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>行业测算</t>
+          <t>行业研究</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4986,7 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>71</v>
+        <v>419</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
@@ -4997,7 +4995,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>2030年预测</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -5009,36 +5007,36 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>全球人形机器人灵巧手市场规模</t>
+          <t>宇树Dex5灵巧手自由度</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>个</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>2030年预测</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>行业研究</t>
+          <t>公司资料</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>宇树Dex5灵巧手自由度</t>
+          <t>宇树Dex5触觉传感器数量</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
@@ -5059,15 +5057,15 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>宇树Dex5触觉传感器数量</t>
+          <t>计算与感知占整机成本</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -5077,37 +5075,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>公司资料</t>
+          <t>行业测算</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>计算与感知占整机成本</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>行业测算</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>说明：力/力矩传感器因与无锡巨蟹直接相关，已由本表移入"3.4 力/力矩传感器环节"。</t>
         </is>
@@ -5910,7 +5883,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>绿的谐波（唯一）</t>
+          <t>市场存在绿的谐波进入Optimus供应链的相关报道</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
@@ -6701,7 +6674,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>5.1 已上市或已完成发行（对应表9）</t>
+          <t>5.1 已上市或已进入发行阶段（对应表9）</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7043,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>科创板，2026年7月2日注册生效</t>
+          <t>科创板，2026年7月2日注册生效；截至2026/8/10已完成注册并进入发行阶段，尚未挂牌</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -9096,7 +9069,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>港交所上市</t>
+          <t>港交所上市（首发）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9128,7 +9101,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>可转换公司债券发行</t>
+          <t>可转换公司债券发行（再融资）</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9160,7 +9133,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026年度定增</t>
+          <t>2026年度定增（再融资）</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -10169,7 +10142,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>约8,000平方米</t>
+          <t>约12,000平方米</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11329,7 +11302,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>成立2019年、8,000平方米基地、江苏省重点智能制造企业；R48/R58/R68/R83/R102/R120六大系列、全系双编码器；R48-Lite参数（Ø48×45.5mm、0.26kg、5N·m/11±0.5N·m、101:1、3,000rpm）；通用型上肢硬件平台、人形机械臂</t>
+          <t>成立2019年、12,000平方米基地、江苏省重点智能制造企业；R48/R58/R68/R83/R102/R120六大系列、全系双编码器；R48-Lite参数（Ø48×45.5mm、0.26kg、5N·m/11±0.5N·m、101:1、3,000rpm）；通用型上肢硬件平台、人形机械臂</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">

--- a/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
+++ b/output/交付物/中国人形机器人产业链研究_图表数据底稿.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>以委托方提供的Wind整理成果为基础重写第六、七章。订正三处：首形科技的主营业务与A2轮跟投主体（应为国泰君安创新投）、智元赴港上市承销团（应为中金＋中信＋摩根士丹利）、卡诺普独家保荐人（应为国泰君安国际）。补充五家国泰海通系公司：三瑞智能、晋拓股份、智谱、镭神技术、飒智智能；补充兆威机电、来福谐波两家已上市产业链公司。新增图7（智元量产爬坡）与图8（国泰海通关联分布）。</t>
+          <t>以Wind数据库为基础重写第六、七章。订正三处：首形科技的主营业务与A2轮跟投主体（应为国泰君安创新投）、智元赴港上市承销团（应为中金＋中信＋摩根士丹利）、卡诺普独家保荐人（应为国泰君安国际）。补充五家国泰海通系公司：三瑞智能、晋拓股份、智谱、镭神技术、飒智智能；补充兆威机电、来福谐波两家已上市产业链公司。新增图7（智元量产爬坡）与图8（国泰海通关联分布）。</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       <c r="E74" s="3" t="inlineStr"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Wind整理成果</t>
+          <t>Wind数据库</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件；各公司年报及公告。本报告复核后补充三瑞智能、兆威机电、来福谐波，并订正绿的谐波、步科股份的保荐机构归属。</t>
+          <t>数据来源：Wind数据库；交易所公开披露文件；各公司年报及公告。本报告复核后补充三瑞智能、兆威机电、来福谐波，并订正绿的谐波、步科股份的保荐机构归属。</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
+          <t>数据来源：Wind数据库；交易所公开披露。本报告复核后补充智元承销团完整名单及乐聚智能出货口径说明。</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>数据来源：Wind整理成果；证监会及各地证监局辅导备案公示；港交所披露文件；公开融资报道及企业工商信息。"券商系股东或投资方"系通过股东穿透与融资报道整理，仅反映券商与企业已有股权层面接触，不代表已建立保荐或辅导关系，两者不可相互推定。</t>
+          <t>数据来源：Wind数据库；证监会及各地证监局辅导备案公示；港交所披露文件；公开融资报道及企业工商信息。"券商系股东或投资方"系通过股东穿透与融资报道整理，仅反映券商与企业已有股权层面接触，不代表已建立保荐或辅导关系，两者不可相互推定。</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6600.HK</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -8947,14 +8947,14 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>本报告新增。连接器；保荐机构以委托方口径列示，未从公开渠道核到发行时保荐主体名称</t>
+          <t>本报告新增。连接器；保荐机构以Wind数据库口径列示，未从公开渠道核到发行时保荐主体名称</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
+          <t>数据来源：Wind数据库；交易所公开披露文件。本报告复核后补充三瑞智能。</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
+          <t>数据来源：Wind数据库；交易所公开披露；证监会及各地证监局辅导备案公示。本报告复核后补充晋拓股份、智谱、镭神技术三家。</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
+          <t>数据来源：Wind数据库；公开融资报道。证券公司私募股权子公司的投资组合并非全部对外披露，本表不构成完整清单。</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>数据来源：委托方提供的Wind整理成果；公开报道。提示：一、上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额；二、投资主体沿革——2026年6月30日海通创新证券投资有限公司吸收合并国泰君安证裕投资有限公司并更名为国泰海通证裕投资有限公司，海通开元投资与国泰君安创新投资的整合亦已启动，本表按交易发生时的名称列示，不作追溯调整。</t>
+          <t>数据来源：Wind数据库；公开报道。提示：一、上述基金多为综合性股权投资基金，机器人仅为投资方向之一，各只基金规模不宜简单加总视为对机器人产业链的投入金额；二、投资主体沿革——2026年6月30日海通创新证券投资有限公司吸收合并国泰君安证裕投资有限公司并更名为国泰海通证裕投资有限公司，海通开元投资与国泰君安创新投资的整合亦已启动，本表按交易发生时的名称列示，不作追溯调整。</t>
         </is>
       </c>
     </row>
